--- a/Sindhi Muslim/Result Sheet/Final Term March-2025/Summative Assessment Final Term Result.xlsx
+++ b/Sindhi Muslim/Result Sheet/Final Term March-2025/Summative Assessment Final Term Result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Result Sheet\Final Term March-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4DCAA1-1D6B-4A62-B4E2-7E5A0F072CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5799147-BEA2-43F0-B1F9-2927B37DD640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ECE (ROSE)" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4031" uniqueCount="938">
   <si>
     <t>GOVERNMENT HIGH SCHOOL SINDHI JAMAAT CO-OPERATIVE HOUSING SOCIETY</t>
   </si>
@@ -2856,6 +2856,12 @@
   </si>
   <si>
     <t>1ST</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
 </sst>
 </file>
@@ -3659,6 +3665,49 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3685,27 +3734,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3743,6 +3771,27 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3750,6 +3799,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3760,9 +3812,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3785,14 +3834,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3801,41 +3842,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4466,6 +4472,126 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>151885</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{268F990F-852A-41FA-A26C-06ABE4DF46FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="219075" y="19050"/>
+          <a:ext cx="409060" cy="504825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>161410</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82261B77-4814-494B-8CCE-C328912771F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="228600" y="28575"/>
+          <a:ext cx="409060" cy="504825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -4826,6 +4952,126 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>104260</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{802E403D-54E3-44BA-9FEA-947F06DBCC69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="171450" y="28575"/>
+          <a:ext cx="409060" cy="504825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>237610</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC58F167-DB81-4C83-8E5D-D1DDDAA0599A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="304800" y="19050"/>
+          <a:ext cx="409060" cy="504825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5140,91 +5386,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="101"/>
-      <c r="T1" s="101"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
     </row>
     <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="101"/>
-      <c r="T2" s="101"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
     </row>
     <row r="3" spans="1:20" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="127" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
-      <c r="R3" s="106"/>
-      <c r="S3" s="106"/>
-      <c r="T3" s="106"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="127"/>
+      <c r="T3" s="127"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="103" t="s">
+      <c r="E4" s="124" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="60"/>
@@ -5239,28 +5485,28 @@
       <c r="M4" s="62"/>
       <c r="N4" s="62"/>
       <c r="O4" s="63"/>
-      <c r="P4" s="103" t="s">
+      <c r="P4" s="124" t="s">
         <v>859</v>
       </c>
-      <c r="Q4" s="103" t="s">
+      <c r="Q4" s="124" t="s">
         <v>118</v>
       </c>
-      <c r="R4" s="103" t="s">
+      <c r="R4" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="S4" s="103" t="s">
+      <c r="S4" s="124" t="s">
         <v>289</v>
       </c>
-      <c r="T4" s="102" t="s">
+      <c r="T4" s="123" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="104"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="125"/>
       <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
@@ -5291,18 +5537,18 @@
       <c r="O5" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="P5" s="104"/>
-      <c r="Q5" s="104"/>
-      <c r="R5" s="104"/>
-      <c r="S5" s="104"/>
-      <c r="T5" s="102"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="125"/>
+      <c r="T5" s="123"/>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="105"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="126"/>
       <c r="F6" s="3" t="s">
         <v>289</v>
       </c>
@@ -5324,8 +5570,8 @@
       <c r="L6" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="M6" s="3">
-        <v>150</v>
+      <c r="M6" s="3" t="s">
+        <v>289</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>289</v>
@@ -5342,32 +5588,32 @@
       <c r="R6" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="S6" s="105"/>
-      <c r="T6" s="102"/>
+      <c r="S6" s="126"/>
+      <c r="T6" s="123"/>
     </row>
     <row r="7" spans="1:20" ht="26.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="98" t="s">
+      <c r="A7" s="119" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="99"/>
-      <c r="O7" s="99"/>
-      <c r="P7" s="99"/>
-      <c r="Q7" s="99"/>
-      <c r="R7" s="99"/>
-      <c r="S7" s="99"/>
-      <c r="T7" s="100"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="120"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="120"/>
+      <c r="K7" s="120"/>
+      <c r="L7" s="120"/>
+      <c r="M7" s="120"/>
+      <c r="N7" s="120"/>
+      <c r="O7" s="120"/>
+      <c r="P7" s="120"/>
+      <c r="Q7" s="120"/>
+      <c r="R7" s="120"/>
+      <c r="S7" s="120"/>
+      <c r="T7" s="121"/>
     </row>
     <row r="8" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="42">
@@ -6796,28 +7042,28 @@
       </c>
     </row>
     <row r="31" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="98" t="s">
+      <c r="A31" s="119" t="s">
         <v>165</v>
       </c>
-      <c r="B31" s="99"/>
-      <c r="C31" s="99"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="99"/>
-      <c r="H31" s="99"/>
-      <c r="I31" s="99"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="99"/>
-      <c r="L31" s="99"/>
-      <c r="M31" s="99"/>
-      <c r="N31" s="99"/>
-      <c r="O31" s="99"/>
-      <c r="P31" s="99"/>
-      <c r="Q31" s="99"/>
-      <c r="R31" s="99"/>
-      <c r="S31" s="99"/>
-      <c r="T31" s="100"/>
+      <c r="B31" s="120"/>
+      <c r="C31" s="120"/>
+      <c r="D31" s="120"/>
+      <c r="E31" s="120"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="120"/>
+      <c r="J31" s="120"/>
+      <c r="K31" s="120"/>
+      <c r="L31" s="120"/>
+      <c r="M31" s="120"/>
+      <c r="N31" s="120"/>
+      <c r="O31" s="120"/>
+      <c r="P31" s="120"/>
+      <c r="Q31" s="120"/>
+      <c r="R31" s="120"/>
+      <c r="S31" s="120"/>
+      <c r="T31" s="121"/>
     </row>
     <row r="32" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="42">
@@ -8719,113 +8965,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="127" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="144" t="s">
+      <c r="F4" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="145"/>
-      <c r="M4" s="146"/>
-      <c r="N4" s="102" t="s">
+      <c r="G4" s="162"/>
+      <c r="H4" s="162"/>
+      <c r="I4" s="162"/>
+      <c r="J4" s="162"/>
+      <c r="K4" s="162"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="163"/>
+      <c r="N4" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="102" t="s">
+      <c r="O4" s="123" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="102" t="s">
+      <c r="P4" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="128" t="s">
+      <c r="Q4" s="149" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="43.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
       <c r="F5" s="2" t="s">
         <v>932</v>
       </c>
@@ -8850,17 +9096,17 @@
       <c r="M5" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="128"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="149"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
       <c r="F6" s="3">
         <v>100</v>
       </c>
@@ -8889,9 +9135,9 @@
         <f>SUM(F6:M6)</f>
         <v>800</v>
       </c>
-      <c r="O6" s="102"/>
-      <c r="P6" s="102"/>
-      <c r="Q6" s="128"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="123"/>
+      <c r="Q6" s="149"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="49">
@@ -8940,7 +9186,7 @@
         <f>SUM(F7:M7)</f>
         <v>618</v>
       </c>
-      <c r="P7" s="154">
+      <c r="P7" s="109">
         <f>O7/N7</f>
         <v>0.77249999999999996</v>
       </c>
@@ -8995,7 +9241,7 @@
         <f t="shared" ref="O8:O50" si="0">SUM(F8:M8)</f>
         <v>321</v>
       </c>
-      <c r="P8" s="154">
+      <c r="P8" s="109">
         <f t="shared" ref="P8:P50" si="1">O8/N8</f>
         <v>0.40125</v>
       </c>
@@ -9004,7 +9250,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="140">
+      <c r="A9" s="98">
         <v>3</v>
       </c>
       <c r="B9" s="37">
@@ -9050,7 +9296,7 @@
         <f t="shared" si="0"/>
         <v>192</v>
       </c>
-      <c r="P9" s="154">
+      <c r="P9" s="109">
         <f t="shared" si="1"/>
         <v>0.24</v>
       </c>
@@ -9105,7 +9351,7 @@
         <f t="shared" si="0"/>
         <v>144</v>
       </c>
-      <c r="P10" s="154">
+      <c r="P10" s="109">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
@@ -9114,7 +9360,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="140">
+      <c r="A11" s="98">
         <v>5</v>
       </c>
       <c r="B11" s="37">
@@ -9160,7 +9406,7 @@
         <f t="shared" si="0"/>
         <v>168</v>
       </c>
-      <c r="P11" s="154">
+      <c r="P11" s="109">
         <f t="shared" si="1"/>
         <v>0.21</v>
       </c>
@@ -9169,7 +9415,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="140">
+      <c r="A12" s="98">
         <v>6</v>
       </c>
       <c r="B12" s="37">
@@ -9215,7 +9461,7 @@
         <f t="shared" si="0"/>
         <v>390</v>
       </c>
-      <c r="P12" s="154">
+      <c r="P12" s="109">
         <f t="shared" si="1"/>
         <v>0.48749999999999999</v>
       </c>
@@ -9224,7 +9470,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="140">
+      <c r="A13" s="98">
         <v>7</v>
       </c>
       <c r="B13" s="37">
@@ -9270,7 +9516,7 @@
         <f t="shared" si="0"/>
         <v>284</v>
       </c>
-      <c r="P13" s="154">
+      <c r="P13" s="109">
         <f t="shared" si="1"/>
         <v>0.35499999999999998</v>
       </c>
@@ -9325,7 +9571,7 @@
         <f t="shared" si="0"/>
         <v>398</v>
       </c>
-      <c r="P14" s="154">
+      <c r="P14" s="109">
         <f t="shared" si="1"/>
         <v>0.4975</v>
       </c>
@@ -9380,7 +9626,7 @@
         <f t="shared" si="0"/>
         <v>454</v>
       </c>
-      <c r="P15" s="154">
+      <c r="P15" s="109">
         <f t="shared" si="1"/>
         <v>0.5675</v>
       </c>
@@ -9435,7 +9681,7 @@
         <f t="shared" si="0"/>
         <v>460</v>
       </c>
-      <c r="P16" s="154">
+      <c r="P16" s="109">
         <f t="shared" si="1"/>
         <v>0.57499999999999996</v>
       </c>
@@ -9490,7 +9736,7 @@
         <f t="shared" si="0"/>
         <v>175</v>
       </c>
-      <c r="P17" s="154">
+      <c r="P17" s="109">
         <f t="shared" si="1"/>
         <v>0.21875</v>
       </c>
@@ -9545,7 +9791,7 @@
         <f t="shared" si="0"/>
         <v>433</v>
       </c>
-      <c r="P18" s="154">
+      <c r="P18" s="109">
         <f t="shared" si="1"/>
         <v>0.54125000000000001</v>
       </c>
@@ -9600,7 +9846,7 @@
         <f t="shared" si="0"/>
         <v>344</v>
       </c>
-      <c r="P19" s="154">
+      <c r="P19" s="109">
         <f t="shared" si="1"/>
         <v>0.43</v>
       </c>
@@ -9655,7 +9901,7 @@
         <f t="shared" si="0"/>
         <v>653</v>
       </c>
-      <c r="P20" s="154">
+      <c r="P20" s="109">
         <f t="shared" si="1"/>
         <v>0.81625000000000003</v>
       </c>
@@ -9710,7 +9956,7 @@
         <f t="shared" si="0"/>
         <v>344</v>
       </c>
-      <c r="P21" s="154">
+      <c r="P21" s="109">
         <f t="shared" si="1"/>
         <v>0.43</v>
       </c>
@@ -9765,7 +10011,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P22" s="154">
+      <c r="P22" s="109">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9820,7 +10066,7 @@
         <f t="shared" si="0"/>
         <v>241</v>
       </c>
-      <c r="P23" s="154">
+      <c r="P23" s="109">
         <f t="shared" si="1"/>
         <v>0.30125000000000002</v>
       </c>
@@ -9875,7 +10121,7 @@
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="P24" s="154">
+      <c r="P24" s="109">
         <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
@@ -9930,7 +10176,7 @@
         <f t="shared" si="0"/>
         <v>493</v>
       </c>
-      <c r="P25" s="154">
+      <c r="P25" s="109">
         <f t="shared" si="1"/>
         <v>0.61624999999999996</v>
       </c>
@@ -9985,7 +10231,7 @@
         <f t="shared" si="0"/>
         <v>352</v>
       </c>
-      <c r="P26" s="154">
+      <c r="P26" s="109">
         <f t="shared" si="1"/>
         <v>0.44</v>
       </c>
@@ -10012,22 +10258,22 @@
       <c r="F27" s="31">
         <v>65</v>
       </c>
-      <c r="G27" s="141">
+      <c r="G27" s="99">
         <v>45</v>
       </c>
-      <c r="H27" s="141">
+      <c r="H27" s="99">
         <v>51</v>
       </c>
-      <c r="I27" s="141">
+      <c r="I27" s="99">
         <v>33</v>
       </c>
-      <c r="J27" s="141">
+      <c r="J27" s="99">
         <v>33</v>
       </c>
-      <c r="K27" s="141">
+      <c r="K27" s="99">
         <v>33</v>
       </c>
-      <c r="L27" s="141">
+      <c r="L27" s="99">
         <v>33</v>
       </c>
       <c r="M27" s="49">
@@ -10040,7 +10286,7 @@
         <f t="shared" si="0"/>
         <v>369</v>
       </c>
-      <c r="P27" s="154">
+      <c r="P27" s="109">
         <f t="shared" si="1"/>
         <v>0.46124999999999999</v>
       </c>
@@ -10095,7 +10341,7 @@
         <f t="shared" si="0"/>
         <v>451</v>
       </c>
-      <c r="P28" s="154">
+      <c r="P28" s="109">
         <f t="shared" si="1"/>
         <v>0.56374999999999997</v>
       </c>
@@ -10150,7 +10396,7 @@
         <f t="shared" si="0"/>
         <v>213</v>
       </c>
-      <c r="P29" s="154">
+      <c r="P29" s="109">
         <f t="shared" si="1"/>
         <v>0.26624999999999999</v>
       </c>
@@ -10159,7 +10405,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="141">
+      <c r="A30" s="99">
         <v>24</v>
       </c>
       <c r="B30" s="37">
@@ -10174,25 +10420,25 @@
       <c r="E30" s="28" t="s">
         <v>666</v>
       </c>
-      <c r="F30" s="150">
+      <c r="F30" s="105">
         <v>90</v>
       </c>
-      <c r="G30" s="141">
+      <c r="G30" s="99">
         <v>59</v>
       </c>
-      <c r="H30" s="141">
+      <c r="H30" s="99">
         <v>71</v>
       </c>
-      <c r="I30" s="141">
+      <c r="I30" s="99">
         <v>92</v>
       </c>
-      <c r="J30" s="141">
+      <c r="J30" s="99">
         <v>84</v>
       </c>
-      <c r="K30" s="141">
+      <c r="K30" s="99">
         <v>71</v>
       </c>
-      <c r="L30" s="141">
+      <c r="L30" s="99">
         <v>94</v>
       </c>
       <c r="M30" s="49">
@@ -10205,7 +10451,7 @@
         <f t="shared" si="0"/>
         <v>660</v>
       </c>
-      <c r="P30" s="154">
+      <c r="P30" s="109">
         <f t="shared" si="1"/>
         <v>0.82499999999999996</v>
       </c>
@@ -10214,7 +10460,7 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="141">
+      <c r="A31" s="99">
         <v>25</v>
       </c>
       <c r="B31" s="37">
@@ -10260,7 +10506,7 @@
         <f t="shared" si="0"/>
         <v>391</v>
       </c>
-      <c r="P31" s="154">
+      <c r="P31" s="109">
         <f t="shared" si="1"/>
         <v>0.48875000000000002</v>
       </c>
@@ -10315,7 +10561,7 @@
         <f t="shared" si="0"/>
         <v>441</v>
       </c>
-      <c r="P32" s="154">
+      <c r="P32" s="109">
         <f t="shared" si="1"/>
         <v>0.55125000000000002</v>
       </c>
@@ -10370,7 +10616,7 @@
         <f t="shared" si="0"/>
         <v>337</v>
       </c>
-      <c r="P33" s="154">
+      <c r="P33" s="109">
         <f t="shared" si="1"/>
         <v>0.42125000000000001</v>
       </c>
@@ -10379,8 +10625,8 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="141">
-        <v>28</v>
+      <c r="A34" s="99">
+        <v>1</v>
       </c>
       <c r="B34" s="37">
         <v>636</v>
@@ -10397,22 +10643,22 @@
       <c r="F34" s="32">
         <v>98</v>
       </c>
-      <c r="G34" s="141">
+      <c r="G34" s="99">
         <v>90</v>
       </c>
-      <c r="H34" s="141">
+      <c r="H34" s="99">
         <v>91</v>
       </c>
-      <c r="I34" s="141">
+      <c r="I34" s="99">
         <v>98</v>
       </c>
-      <c r="J34" s="141">
+      <c r="J34" s="99">
         <v>97</v>
       </c>
-      <c r="K34" s="141">
+      <c r="K34" s="99">
         <v>98</v>
       </c>
-      <c r="L34" s="141">
+      <c r="L34" s="99">
         <v>98</v>
       </c>
       <c r="M34" s="49">
@@ -10425,7 +10671,7 @@
         <f t="shared" si="0"/>
         <v>766</v>
       </c>
-      <c r="P34" s="154">
+      <c r="P34" s="109">
         <f t="shared" si="1"/>
         <v>0.95750000000000002</v>
       </c>
@@ -10435,7 +10681,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="49">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="B35" s="37">
         <v>862</v>
@@ -10480,7 +10726,7 @@
         <f t="shared" si="0"/>
         <v>611</v>
       </c>
-      <c r="P35" s="154">
+      <c r="P35" s="109">
         <f t="shared" si="1"/>
         <v>0.76375000000000004</v>
       </c>
@@ -10489,8 +10735,8 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="52">
-        <v>30</v>
+      <c r="A36" s="99">
+        <v>3</v>
       </c>
       <c r="B36" s="38">
         <v>870</v>
@@ -10504,25 +10750,25 @@
       <c r="E36" s="28" t="s">
         <v>666</v>
       </c>
-      <c r="F36" s="151">
+      <c r="F36" s="106">
         <v>95</v>
       </c>
-      <c r="G36" s="141">
+      <c r="G36" s="99">
         <v>85</v>
       </c>
-      <c r="H36" s="141">
+      <c r="H36" s="99">
         <v>82</v>
       </c>
-      <c r="I36" s="141">
+      <c r="I36" s="99">
         <v>90</v>
       </c>
-      <c r="J36" s="141">
+      <c r="J36" s="99">
         <v>82</v>
       </c>
-      <c r="K36" s="141">
+      <c r="K36" s="99">
         <v>79</v>
       </c>
-      <c r="L36" s="141">
+      <c r="L36" s="99">
         <v>93</v>
       </c>
       <c r="M36" s="49">
@@ -10535,7 +10781,7 @@
         <f t="shared" si="0"/>
         <v>705</v>
       </c>
-      <c r="P36" s="154">
+      <c r="P36" s="109">
         <f t="shared" si="1"/>
         <v>0.88124999999999998</v>
       </c>
@@ -10544,8 +10790,8 @@
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="52">
-        <v>31</v>
+      <c r="A37" s="49">
+        <v>4</v>
       </c>
       <c r="B37" s="38">
         <v>626</v>
@@ -10590,7 +10836,7 @@
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="P37" s="154">
+      <c r="P37" s="109">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -10599,8 +10845,8 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="49">
-        <v>33</v>
+      <c r="A38" s="99">
+        <v>5</v>
       </c>
       <c r="B38" s="38">
         <v>871</v>
@@ -10614,7 +10860,7 @@
       <c r="E38" s="28" t="s">
         <v>666</v>
       </c>
-      <c r="F38" s="152">
+      <c r="F38" s="107">
         <v>75</v>
       </c>
       <c r="G38" s="52">
@@ -10645,7 +10891,7 @@
         <f t="shared" si="0"/>
         <v>624</v>
       </c>
-      <c r="P38" s="154">
+      <c r="P38" s="109">
         <f t="shared" si="1"/>
         <v>0.78</v>
       </c>
@@ -10655,7 +10901,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="49">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B39" s="38">
         <v>637</v>
@@ -10700,7 +10946,7 @@
         <f t="shared" si="0"/>
         <v>708</v>
       </c>
-      <c r="P39" s="154">
+      <c r="P39" s="109">
         <f t="shared" si="1"/>
         <v>0.88500000000000001</v>
       </c>
@@ -10709,8 +10955,8 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="49">
-        <v>35</v>
+      <c r="A40" s="99">
+        <v>7</v>
       </c>
       <c r="B40" s="38">
         <v>720</v>
@@ -10724,7 +10970,7 @@
       <c r="E40" s="28" t="s">
         <v>666</v>
       </c>
-      <c r="F40" s="152">
+      <c r="F40" s="107">
         <v>97</v>
       </c>
       <c r="G40" s="52">
@@ -10755,7 +11001,7 @@
         <f t="shared" si="0"/>
         <v>621</v>
       </c>
-      <c r="P40" s="154">
+      <c r="P40" s="109">
         <f t="shared" si="1"/>
         <v>0.77625</v>
       </c>
@@ -10765,7 +11011,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="49">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B41" s="38">
         <v>722</v>
@@ -10779,25 +11025,25 @@
       <c r="E41" s="28" t="s">
         <v>666</v>
       </c>
-      <c r="F41" s="151">
+      <c r="F41" s="106">
         <v>99</v>
       </c>
-      <c r="G41" s="141">
+      <c r="G41" s="99">
         <v>54</v>
       </c>
-      <c r="H41" s="141">
+      <c r="H41" s="99">
         <v>87</v>
       </c>
-      <c r="I41" s="141">
+      <c r="I41" s="99">
         <v>75</v>
       </c>
-      <c r="J41" s="141">
+      <c r="J41" s="99">
         <v>85</v>
       </c>
-      <c r="K41" s="141">
+      <c r="K41" s="99">
         <v>86</v>
       </c>
-      <c r="L41" s="141">
+      <c r="L41" s="99">
         <v>95</v>
       </c>
       <c r="M41" s="49">
@@ -10810,7 +11056,7 @@
         <f t="shared" si="0"/>
         <v>678</v>
       </c>
-      <c r="P41" s="154">
+      <c r="P41" s="109">
         <f t="shared" si="1"/>
         <v>0.84750000000000003</v>
       </c>
@@ -10819,8 +11065,8 @@
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="49">
-        <v>37</v>
+      <c r="A42" s="99">
+        <v>9</v>
       </c>
       <c r="B42" s="38">
         <v>352</v>
@@ -10865,7 +11111,7 @@
         <f t="shared" si="0"/>
         <v>401</v>
       </c>
-      <c r="P42" s="154">
+      <c r="P42" s="109">
         <f t="shared" si="1"/>
         <v>0.50124999999999997</v>
       </c>
@@ -10875,7 +11121,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="49">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="B43" s="38">
         <v>350</v>
@@ -10920,7 +11166,7 @@
         <f t="shared" si="0"/>
         <v>290</v>
       </c>
-      <c r="P43" s="154">
+      <c r="P43" s="109">
         <f t="shared" si="1"/>
         <v>0.36249999999999999</v>
       </c>
@@ -10929,8 +11175,8 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="49">
-        <v>39</v>
+      <c r="A44" s="99">
+        <v>11</v>
       </c>
       <c r="B44" s="38">
         <v>629</v>
@@ -10944,25 +11190,25 @@
       <c r="E44" s="28" t="s">
         <v>666</v>
       </c>
-      <c r="F44" s="151">
+      <c r="F44" s="106">
         <v>99</v>
       </c>
-      <c r="G44" s="141">
+      <c r="G44" s="99">
         <v>66</v>
       </c>
-      <c r="H44" s="141">
+      <c r="H44" s="99">
         <v>33</v>
       </c>
-      <c r="I44" s="141">
+      <c r="I44" s="99">
         <v>93</v>
       </c>
-      <c r="J44" s="141">
+      <c r="J44" s="99">
         <v>90</v>
       </c>
-      <c r="K44" s="141">
+      <c r="K44" s="99">
         <v>74</v>
       </c>
-      <c r="L44" s="141">
+      <c r="L44" s="99">
         <v>67</v>
       </c>
       <c r="M44" s="49">
@@ -10975,7 +11221,7 @@
         <f t="shared" si="0"/>
         <v>617</v>
       </c>
-      <c r="P44" s="154">
+      <c r="P44" s="109">
         <f t="shared" si="1"/>
         <v>0.77124999999999999</v>
       </c>
@@ -10985,7 +11231,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="49">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="B45" s="38">
         <v>726</v>
@@ -11002,22 +11248,22 @@
       <c r="F45" s="39">
         <v>40</v>
       </c>
-      <c r="G45" s="153">
+      <c r="G45" s="108">
         <v>43</v>
       </c>
-      <c r="H45" s="153">
+      <c r="H45" s="108">
         <v>27</v>
       </c>
-      <c r="I45" s="153">
+      <c r="I45" s="108">
         <v>66</v>
       </c>
-      <c r="J45" s="153">
+      <c r="J45" s="108">
         <v>27</v>
       </c>
-      <c r="K45" s="153">
+      <c r="K45" s="108">
         <v>33</v>
       </c>
-      <c r="L45" s="153">
+      <c r="L45" s="108">
         <v>36</v>
       </c>
       <c r="M45" s="49">
@@ -11030,7 +11276,7 @@
         <f t="shared" si="0"/>
         <v>324</v>
       </c>
-      <c r="P45" s="154">
+      <c r="P45" s="109">
         <f t="shared" si="1"/>
         <v>0.40500000000000003</v>
       </c>
@@ -11039,8 +11285,8 @@
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="52">
-        <v>41</v>
+      <c r="A46" s="99">
+        <v>13</v>
       </c>
       <c r="B46" s="38">
         <v>726</v>
@@ -11057,22 +11303,22 @@
       <c r="F46" s="39">
         <v>45</v>
       </c>
-      <c r="G46" s="153" t="s">
-        <v>807</v>
-      </c>
-      <c r="H46" s="153">
+      <c r="G46" s="108" t="s">
+        <v>807</v>
+      </c>
+      <c r="H46" s="108">
         <v>10</v>
       </c>
-      <c r="I46" s="153">
+      <c r="I46" s="108">
         <v>3</v>
       </c>
-      <c r="J46" s="153">
+      <c r="J46" s="108">
         <v>8</v>
       </c>
-      <c r="K46" s="153">
-        <v>5</v>
-      </c>
-      <c r="L46" s="153">
+      <c r="K46" s="108">
+        <v>5</v>
+      </c>
+      <c r="L46" s="108">
         <v>0</v>
       </c>
       <c r="M46" s="49">
@@ -11085,7 +11331,7 @@
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="P46" s="154">
+      <c r="P46" s="109">
         <f t="shared" si="1"/>
         <v>0.16500000000000001</v>
       </c>
@@ -11095,7 +11341,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="49">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="B47" s="38">
         <v>390</v>
@@ -11140,7 +11386,7 @@
         <f t="shared" si="0"/>
         <v>574</v>
       </c>
-      <c r="P47" s="154">
+      <c r="P47" s="109">
         <f t="shared" si="1"/>
         <v>0.71750000000000003</v>
       </c>
@@ -11149,8 +11395,8 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="49">
-        <v>43</v>
+      <c r="A48" s="99">
+        <v>15</v>
       </c>
       <c r="B48" s="38">
         <v>357</v>
@@ -11195,7 +11441,7 @@
         <f t="shared" si="0"/>
         <v>358</v>
       </c>
-      <c r="P48" s="154">
+      <c r="P48" s="109">
         <f t="shared" si="1"/>
         <v>0.44750000000000001</v>
       </c>
@@ -11204,8 +11450,8 @@
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="141">
-        <v>44</v>
+      <c r="A49" s="49">
+        <v>16</v>
       </c>
       <c r="B49" s="38">
         <v>623</v>
@@ -11219,7 +11465,7 @@
       <c r="E49" s="28" t="s">
         <v>666</v>
       </c>
-      <c r="F49" s="152">
+      <c r="F49" s="107">
         <v>99</v>
       </c>
       <c r="G49" s="52">
@@ -11250,7 +11496,7 @@
         <f t="shared" si="0"/>
         <v>779</v>
       </c>
-      <c r="P49" s="154">
+      <c r="P49" s="109">
         <f t="shared" si="1"/>
         <v>0.97375</v>
       </c>
@@ -11259,8 +11505,8 @@
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="49">
-        <v>45</v>
+      <c r="A50" s="99">
+        <v>17</v>
       </c>
       <c r="B50" s="38">
         <v>905</v>
@@ -11305,7 +11551,7 @@
         <f t="shared" si="0"/>
         <v>735</v>
       </c>
-      <c r="P50" s="154">
+      <c r="P50" s="109">
         <f t="shared" si="1"/>
         <v>0.91874999999999996</v>
       </c>
@@ -11343,6 +11589,7 @@
   <ignoredErrors>
     <ignoredError sqref="O7:O50" formulaRange="1"/>
   </ignoredErrors>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -11361,113 +11608,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="127" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="128" t="s">
+      <c r="F4" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="102" t="s">
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="102" t="s">
+      <c r="O4" s="123" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="102" t="s">
+      <c r="P4" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="128" t="s">
+      <c r="Q4" s="149" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="43.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
@@ -11492,17 +11739,17 @@
       <c r="M5" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="128"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="149"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
       <c r="F6" s="3">
         <v>100</v>
       </c>
@@ -11531,15 +11778,15 @@
         <f>SUM(F6:M6)</f>
         <v>800</v>
       </c>
-      <c r="O6" s="102"/>
-      <c r="P6" s="102"/>
-      <c r="Q6" s="128"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="123"/>
+      <c r="Q6" s="149"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="25">
         <v>1</v>
       </c>
-      <c r="B7" s="155">
+      <c r="B7" s="110">
         <v>737</v>
       </c>
       <c r="C7" s="88" t="s">
@@ -11582,7 +11829,7 @@
         <f>SUM(F7:M7)</f>
         <v>467</v>
       </c>
-      <c r="P7" s="163">
+      <c r="P7" s="118">
         <f>O7/N7</f>
         <v>0.58374999999999999</v>
       </c>
@@ -11594,7 +11841,7 @@
       <c r="A8" s="25">
         <v>2</v>
       </c>
-      <c r="B8" s="155">
+      <c r="B8" s="110">
         <v>734</v>
       </c>
       <c r="C8" s="88" t="s">
@@ -11637,7 +11884,7 @@
         <f t="shared" ref="O8:O45" si="0">SUM(F8:M8)</f>
         <v>433</v>
       </c>
-      <c r="P8" s="163">
+      <c r="P8" s="118">
         <f t="shared" ref="P8:P45" si="1">O8/N8</f>
         <v>0.54125000000000001</v>
       </c>
@@ -11646,10 +11893,10 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="156">
+      <c r="A9" s="111">
         <v>3</v>
       </c>
-      <c r="B9" s="155">
+      <c r="B9" s="110">
         <v>787</v>
       </c>
       <c r="C9" s="88" t="s">
@@ -11692,7 +11939,7 @@
         <f t="shared" si="0"/>
         <v>638</v>
       </c>
-      <c r="P9" s="163">
+      <c r="P9" s="118">
         <f t="shared" si="1"/>
         <v>0.79749999999999999</v>
       </c>
@@ -11704,7 +11951,7 @@
       <c r="A10" s="25">
         <v>4</v>
       </c>
-      <c r="B10" s="155">
+      <c r="B10" s="110">
         <v>742</v>
       </c>
       <c r="C10" s="88" t="s">
@@ -11747,7 +11994,7 @@
         <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="P10" s="163">
+      <c r="P10" s="118">
         <f t="shared" si="1"/>
         <v>0.4375</v>
       </c>
@@ -11756,10 +12003,10 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="156">
-        <v>5</v>
-      </c>
-      <c r="B11" s="155">
+      <c r="A11" s="111">
+        <v>5</v>
+      </c>
+      <c r="B11" s="110">
         <v>740</v>
       </c>
       <c r="C11" s="88" t="s">
@@ -11802,7 +12049,7 @@
         <f t="shared" si="0"/>
         <v>305</v>
       </c>
-      <c r="P11" s="163">
+      <c r="P11" s="118">
         <f t="shared" si="1"/>
         <v>0.38124999999999998</v>
       </c>
@@ -11811,10 +12058,10 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="156">
+      <c r="A12" s="111">
         <v>6</v>
       </c>
-      <c r="B12" s="155">
+      <c r="B12" s="110">
         <v>738</v>
       </c>
       <c r="C12" s="88" t="s">
@@ -11857,7 +12104,7 @@
         <f t="shared" si="0"/>
         <v>314</v>
       </c>
-      <c r="P12" s="163">
+      <c r="P12" s="118">
         <f t="shared" si="1"/>
         <v>0.39250000000000002</v>
       </c>
@@ -11866,10 +12113,10 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="156">
+      <c r="A13" s="111">
         <v>7</v>
       </c>
-      <c r="B13" s="155">
+      <c r="B13" s="110">
         <v>739</v>
       </c>
       <c r="C13" s="88" t="s">
@@ -11912,7 +12159,7 @@
         <f t="shared" si="0"/>
         <v>336</v>
       </c>
-      <c r="P13" s="163">
+      <c r="P13" s="118">
         <f t="shared" si="1"/>
         <v>0.42</v>
       </c>
@@ -11924,7 +12171,7 @@
       <c r="A14" s="25">
         <v>8</v>
       </c>
-      <c r="B14" s="155">
+      <c r="B14" s="110">
         <v>743</v>
       </c>
       <c r="C14" s="88" t="s">
@@ -11967,7 +12214,7 @@
         <f t="shared" si="0"/>
         <v>643</v>
       </c>
-      <c r="P14" s="163">
+      <c r="P14" s="118">
         <f t="shared" si="1"/>
         <v>0.80374999999999996</v>
       </c>
@@ -11979,7 +12226,7 @@
       <c r="A15" s="25">
         <v>9</v>
       </c>
-      <c r="B15" s="155">
+      <c r="B15" s="110">
         <v>729</v>
       </c>
       <c r="C15" s="88" t="s">
@@ -12022,7 +12269,7 @@
         <f t="shared" si="0"/>
         <v>355</v>
       </c>
-      <c r="P15" s="163">
+      <c r="P15" s="118">
         <f t="shared" si="1"/>
         <v>0.44374999999999998</v>
       </c>
@@ -12034,7 +12281,7 @@
       <c r="A16" s="25">
         <v>10</v>
       </c>
-      <c r="B16" s="155">
+      <c r="B16" s="110">
         <v>735</v>
       </c>
       <c r="C16" s="88" t="s">
@@ -12077,7 +12324,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P16" s="163">
+      <c r="P16" s="118">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -12089,7 +12336,7 @@
       <c r="A17" s="25">
         <v>11</v>
       </c>
-      <c r="B17" s="155">
+      <c r="B17" s="110">
         <v>736</v>
       </c>
       <c r="C17" s="88" t="s">
@@ -12132,7 +12379,7 @@
         <f t="shared" si="0"/>
         <v>665</v>
       </c>
-      <c r="P17" s="163">
+      <c r="P17" s="118">
         <f t="shared" si="1"/>
         <v>0.83125000000000004</v>
       </c>
@@ -12144,7 +12391,7 @@
       <c r="A18" s="25">
         <v>12</v>
       </c>
-      <c r="B18" s="155">
+      <c r="B18" s="110">
         <v>759</v>
       </c>
       <c r="C18" s="88" t="s">
@@ -12187,7 +12434,7 @@
         <f t="shared" si="0"/>
         <v>458</v>
       </c>
-      <c r="P18" s="163">
+      <c r="P18" s="118">
         <f t="shared" si="1"/>
         <v>0.57250000000000001</v>
       </c>
@@ -12199,7 +12446,7 @@
       <c r="A19" s="25">
         <v>13</v>
       </c>
-      <c r="B19" s="155">
+      <c r="B19" s="110">
         <v>746</v>
       </c>
       <c r="C19" s="88" t="s">
@@ -12242,7 +12489,7 @@
         <f t="shared" si="0"/>
         <v>624</v>
       </c>
-      <c r="P19" s="163">
+      <c r="P19" s="118">
         <f t="shared" si="1"/>
         <v>0.78</v>
       </c>
@@ -12254,7 +12501,7 @@
       <c r="A20" s="25">
         <v>14</v>
       </c>
-      <c r="B20" s="155">
+      <c r="B20" s="110">
         <v>745</v>
       </c>
       <c r="C20" s="88" t="s">
@@ -12297,7 +12544,7 @@
         <f t="shared" si="0"/>
         <v>672</v>
       </c>
-      <c r="P20" s="163">
+      <c r="P20" s="118">
         <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
@@ -12309,7 +12556,7 @@
       <c r="A21" s="25">
         <v>15</v>
       </c>
-      <c r="B21" s="155">
+      <c r="B21" s="110">
         <v>731</v>
       </c>
       <c r="C21" s="88" t="s">
@@ -12352,7 +12599,7 @@
         <f t="shared" si="0"/>
         <v>451</v>
       </c>
-      <c r="P21" s="163">
+      <c r="P21" s="118">
         <f t="shared" si="1"/>
         <v>0.56374999999999997</v>
       </c>
@@ -12364,7 +12611,7 @@
       <c r="A22" s="25">
         <v>16</v>
       </c>
-      <c r="B22" s="155">
+      <c r="B22" s="110">
         <v>788</v>
       </c>
       <c r="C22" s="88" t="s">
@@ -12407,7 +12654,7 @@
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="P22" s="163">
+      <c r="P22" s="118">
         <f t="shared" si="1"/>
         <v>0.10875</v>
       </c>
@@ -12419,7 +12666,7 @@
       <c r="A23" s="25">
         <v>17</v>
       </c>
-      <c r="B23" s="155">
+      <c r="B23" s="110">
         <v>856</v>
       </c>
       <c r="C23" s="88" t="s">
@@ -12462,7 +12709,7 @@
         <f t="shared" si="0"/>
         <v>488</v>
       </c>
-      <c r="P23" s="163">
+      <c r="P23" s="118">
         <f t="shared" si="1"/>
         <v>0.61</v>
       </c>
@@ -12474,7 +12721,7 @@
       <c r="A24" s="25">
         <v>18</v>
       </c>
-      <c r="B24" s="155">
+      <c r="B24" s="110">
         <v>906</v>
       </c>
       <c r="C24" s="88" t="s">
@@ -12517,7 +12764,7 @@
         <f t="shared" si="0"/>
         <v>472</v>
       </c>
-      <c r="P24" s="163">
+      <c r="P24" s="118">
         <f t="shared" si="1"/>
         <v>0.59</v>
       </c>
@@ -12529,7 +12776,7 @@
       <c r="A25" s="25">
         <v>19</v>
       </c>
-      <c r="B25" s="155">
+      <c r="B25" s="110">
         <v>866</v>
       </c>
       <c r="C25" s="88" t="s">
@@ -12572,7 +12819,7 @@
         <f t="shared" si="0"/>
         <v>296</v>
       </c>
-      <c r="P25" s="163">
+      <c r="P25" s="118">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
@@ -12584,7 +12831,7 @@
       <c r="A26" s="25">
         <v>20</v>
       </c>
-      <c r="B26" s="155">
+      <c r="B26" s="110">
         <v>846</v>
       </c>
       <c r="C26" s="88" t="s">
@@ -12627,7 +12874,7 @@
         <f t="shared" si="0"/>
         <v>442</v>
       </c>
-      <c r="P26" s="163">
+      <c r="P26" s="118">
         <f t="shared" si="1"/>
         <v>0.55249999999999999</v>
       </c>
@@ -12639,7 +12886,7 @@
       <c r="A27" s="25">
         <v>21</v>
       </c>
-      <c r="B27" s="155">
+      <c r="B27" s="110">
         <v>857</v>
       </c>
       <c r="C27" s="88" t="s">
@@ -12682,7 +12929,7 @@
         <f t="shared" si="0"/>
         <v>468</v>
       </c>
-      <c r="P27" s="163">
+      <c r="P27" s="118">
         <f t="shared" si="1"/>
         <v>0.58499999999999996</v>
       </c>
@@ -12692,9 +12939,9 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="25">
-        <v>23</v>
-      </c>
-      <c r="B28" s="155">
+        <v>1</v>
+      </c>
+      <c r="B28" s="110">
         <v>730</v>
       </c>
       <c r="C28" s="88" t="s">
@@ -12737,7 +12984,7 @@
         <f t="shared" si="0"/>
         <v>395</v>
       </c>
-      <c r="P28" s="163">
+      <c r="P28" s="118">
         <f t="shared" si="1"/>
         <v>0.49375000000000002</v>
       </c>
@@ -12747,9 +12994,9 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="97">
-        <v>24</v>
-      </c>
-      <c r="B29" s="155">
+        <v>2</v>
+      </c>
+      <c r="B29" s="110">
         <v>732</v>
       </c>
       <c r="C29" s="88" t="s">
@@ -12792,7 +13039,7 @@
         <f t="shared" si="0"/>
         <v>476</v>
       </c>
-      <c r="P29" s="163">
+      <c r="P29" s="118">
         <f t="shared" si="1"/>
         <v>0.59499999999999997</v>
       </c>
@@ -12802,9 +13049,9 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="25">
-        <v>25</v>
-      </c>
-      <c r="B30" s="155">
+        <v>3</v>
+      </c>
+      <c r="B30" s="110">
         <v>728</v>
       </c>
       <c r="C30" s="88" t="s">
@@ -12847,7 +13094,7 @@
         <f t="shared" si="0"/>
         <v>725</v>
       </c>
-      <c r="P30" s="163">
+      <c r="P30" s="118">
         <f t="shared" si="1"/>
         <v>0.90625</v>
       </c>
@@ -12856,10 +13103,10 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="25">
-        <v>26</v>
-      </c>
-      <c r="B31" s="155">
+      <c r="A31" s="97">
+        <v>4</v>
+      </c>
+      <c r="B31" s="110">
         <v>760</v>
       </c>
       <c r="C31" s="88" t="s">
@@ -12902,7 +13149,7 @@
         <f t="shared" si="0"/>
         <v>275</v>
       </c>
-      <c r="P31" s="163">
+      <c r="P31" s="118">
         <f t="shared" si="1"/>
         <v>0.34375</v>
       </c>
@@ -12911,10 +13158,10 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="85">
-        <v>27</v>
-      </c>
-      <c r="B32" s="155">
+      <c r="A32" s="25">
+        <v>5</v>
+      </c>
+      <c r="B32" s="110">
         <v>741</v>
       </c>
       <c r="C32" s="88" t="s">
@@ -12957,7 +13204,7 @@
         <f t="shared" si="0"/>
         <v>561</v>
       </c>
-      <c r="P32" s="163">
+      <c r="P32" s="118">
         <f t="shared" si="1"/>
         <v>0.70125000000000004</v>
       </c>
@@ -12966,10 +13213,10 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="25">
-        <v>29</v>
-      </c>
-      <c r="B33" s="155">
+      <c r="A33" s="97">
+        <v>6</v>
+      </c>
+      <c r="B33" s="110">
         <v>744</v>
       </c>
       <c r="C33" s="24" t="s">
@@ -13012,7 +13259,7 @@
         <f t="shared" si="0"/>
         <v>610</v>
       </c>
-      <c r="P33" s="163">
+      <c r="P33" s="118">
         <f t="shared" si="1"/>
         <v>0.76249999999999996</v>
       </c>
@@ -13021,13 +13268,13 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="85">
-        <v>30</v>
-      </c>
-      <c r="B34" s="155">
+      <c r="A34" s="25">
+        <v>7</v>
+      </c>
+      <c r="B34" s="110">
         <v>850</v>
       </c>
-      <c r="C34" s="157" t="s">
+      <c r="C34" s="112" t="s">
         <v>719</v>
       </c>
       <c r="D34" s="90" t="s">
@@ -13067,7 +13314,7 @@
         <f t="shared" si="0"/>
         <v>524</v>
       </c>
-      <c r="P34" s="163">
+      <c r="P34" s="118">
         <f t="shared" si="1"/>
         <v>0.65500000000000003</v>
       </c>
@@ -13076,16 +13323,16 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="85">
-        <v>31</v>
-      </c>
-      <c r="B35" s="155">
+      <c r="A35" s="97">
+        <v>8</v>
+      </c>
+      <c r="B35" s="110">
         <v>767</v>
       </c>
-      <c r="C35" s="158" t="s">
+      <c r="C35" s="113" t="s">
         <v>83</v>
       </c>
-      <c r="D35" s="159" t="s">
+      <c r="D35" s="114" t="s">
         <v>720</v>
       </c>
       <c r="E35" s="87" t="s">
@@ -13122,7 +13369,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P35" s="163">
+      <c r="P35" s="118">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13132,15 +13379,15 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="25">
-        <v>32</v>
-      </c>
-      <c r="B36" s="155">
+        <v>9</v>
+      </c>
+      <c r="B36" s="110">
         <v>875</v>
       </c>
-      <c r="C36" s="158" t="s">
+      <c r="C36" s="113" t="s">
         <v>721</v>
       </c>
-      <c r="D36" s="159" t="s">
+      <c r="D36" s="114" t="s">
         <v>534</v>
       </c>
       <c r="E36" s="87" t="s">
@@ -13177,7 +13424,7 @@
         <f t="shared" si="0"/>
         <v>548</v>
       </c>
-      <c r="P36" s="163">
+      <c r="P36" s="118">
         <f t="shared" si="1"/>
         <v>0.68500000000000005</v>
       </c>
@@ -13186,16 +13433,16 @@
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="25">
-        <v>33</v>
-      </c>
-      <c r="B37" s="155">
+      <c r="A37" s="97">
+        <v>10</v>
+      </c>
+      <c r="B37" s="110">
         <v>727</v>
       </c>
-      <c r="C37" s="158" t="s">
+      <c r="C37" s="113" t="s">
         <v>722</v>
       </c>
-      <c r="D37" s="159" t="s">
+      <c r="D37" s="114" t="s">
         <v>652</v>
       </c>
       <c r="E37" s="87" t="s">
@@ -13232,7 +13479,7 @@
         <f t="shared" si="0"/>
         <v>538</v>
       </c>
-      <c r="P37" s="163">
+      <c r="P37" s="118">
         <f t="shared" si="1"/>
         <v>0.67249999999999999</v>
       </c>
@@ -13242,15 +13489,15 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="25">
-        <v>34</v>
-      </c>
-      <c r="B38" s="155">
+        <v>11</v>
+      </c>
+      <c r="B38" s="110">
         <v>880</v>
       </c>
-      <c r="C38" s="158" t="s">
+      <c r="C38" s="113" t="s">
         <v>723</v>
       </c>
-      <c r="D38" s="159" t="s">
+      <c r="D38" s="114" t="s">
         <v>724</v>
       </c>
       <c r="E38" s="87" t="s">
@@ -13287,7 +13534,7 @@
         <f t="shared" si="0"/>
         <v>477</v>
       </c>
-      <c r="P38" s="163">
+      <c r="P38" s="118">
         <f t="shared" si="1"/>
         <v>0.59624999999999995</v>
       </c>
@@ -13296,16 +13543,16 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="25">
-        <v>35</v>
-      </c>
-      <c r="B39" s="155">
+      <c r="A39" s="97">
+        <v>12</v>
+      </c>
+      <c r="B39" s="110">
         <v>777</v>
       </c>
-      <c r="C39" s="158" t="s">
+      <c r="C39" s="113" t="s">
         <v>725</v>
       </c>
-      <c r="D39" s="159" t="s">
+      <c r="D39" s="114" t="s">
         <v>726</v>
       </c>
       <c r="E39" s="87" t="s">
@@ -13342,7 +13589,7 @@
         <f t="shared" si="0"/>
         <v>490</v>
       </c>
-      <c r="P39" s="163">
+      <c r="P39" s="118">
         <f t="shared" si="1"/>
         <v>0.61250000000000004</v>
       </c>
@@ -13352,15 +13599,15 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
-        <v>36</v>
-      </c>
-      <c r="B40" s="155">
+        <v>13</v>
+      </c>
+      <c r="B40" s="110">
         <v>873</v>
       </c>
-      <c r="C40" s="158" t="s">
+      <c r="C40" s="113" t="s">
         <v>727</v>
       </c>
-      <c r="D40" s="159" t="s">
+      <c r="D40" s="114" t="s">
         <v>32</v>
       </c>
       <c r="E40" s="87" t="s">
@@ -13397,7 +13644,7 @@
         <f t="shared" si="0"/>
         <v>365.5</v>
       </c>
-      <c r="P40" s="163">
+      <c r="P40" s="118">
         <f t="shared" si="1"/>
         <v>0.45687499999999998</v>
       </c>
@@ -13406,16 +13653,16 @@
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="25">
-        <v>37</v>
-      </c>
-      <c r="B41" s="155">
+      <c r="A41" s="97">
+        <v>14</v>
+      </c>
+      <c r="B41" s="110">
         <v>909</v>
       </c>
-      <c r="C41" s="158" t="s">
+      <c r="C41" s="113" t="s">
         <v>728</v>
       </c>
-      <c r="D41" s="159" t="s">
+      <c r="D41" s="114" t="s">
         <v>729</v>
       </c>
       <c r="E41" s="87" t="s">
@@ -13452,7 +13699,7 @@
         <f t="shared" si="0"/>
         <v>315</v>
       </c>
-      <c r="P41" s="163">
+      <c r="P41" s="118">
         <f t="shared" si="1"/>
         <v>0.39374999999999999</v>
       </c>
@@ -13462,15 +13709,15 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
-        <v>38</v>
-      </c>
-      <c r="B42" s="155">
+        <v>15</v>
+      </c>
+      <c r="B42" s="110">
         <v>854</v>
       </c>
-      <c r="C42" s="158" t="s">
+      <c r="C42" s="113" t="s">
         <v>730</v>
       </c>
-      <c r="D42" s="159" t="s">
+      <c r="D42" s="114" t="s">
         <v>731</v>
       </c>
       <c r="E42" s="87" t="s">
@@ -13507,7 +13754,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P42" s="163">
+      <c r="P42" s="118">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -13516,16 +13763,16 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="25">
-        <v>39</v>
-      </c>
-      <c r="B43" s="155">
+      <c r="A43" s="97">
+        <v>16</v>
+      </c>
+      <c r="B43" s="110">
         <v>863</v>
       </c>
-      <c r="C43" s="158" t="s">
+      <c r="C43" s="113" t="s">
         <v>732</v>
       </c>
-      <c r="D43" s="159" t="s">
+      <c r="D43" s="114" t="s">
         <v>733</v>
       </c>
       <c r="E43" s="87" t="s">
@@ -13562,7 +13809,7 @@
         <f t="shared" si="0"/>
         <v>221</v>
       </c>
-      <c r="P43" s="163">
+      <c r="P43" s="118">
         <f t="shared" si="1"/>
         <v>0.27625</v>
       </c>
@@ -13572,15 +13819,15 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="25">
-        <v>40</v>
-      </c>
-      <c r="B44" s="160">
+        <v>17</v>
+      </c>
+      <c r="B44" s="115">
         <v>902</v>
       </c>
-      <c r="C44" s="161" t="s">
+      <c r="C44" s="116" t="s">
         <v>284</v>
       </c>
-      <c r="D44" s="162" t="s">
+      <c r="D44" s="117" t="s">
         <v>734</v>
       </c>
       <c r="E44" s="87" t="s">
@@ -13617,7 +13864,7 @@
         <f t="shared" si="0"/>
         <v>476</v>
       </c>
-      <c r="P44" s="163">
+      <c r="P44" s="118">
         <f t="shared" si="1"/>
         <v>0.59499999999999997</v>
       </c>
@@ -13626,16 +13873,16 @@
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="25">
-        <v>41</v>
-      </c>
-      <c r="B45" s="155">
+      <c r="A45" s="97">
+        <v>18</v>
+      </c>
+      <c r="B45" s="110">
         <v>886</v>
       </c>
-      <c r="C45" s="158" t="s">
+      <c r="C45" s="113" t="s">
         <v>735</v>
       </c>
-      <c r="D45" s="159" t="s">
+      <c r="D45" s="114" t="s">
         <v>736</v>
       </c>
       <c r="E45" s="87" t="s">
@@ -13672,7 +13919,7 @@
         <f t="shared" si="0"/>
         <v>199</v>
       </c>
-      <c r="P45" s="163">
+      <c r="P45" s="118">
         <f t="shared" si="1"/>
         <v>0.24875</v>
       </c>
@@ -13719,6 +13966,7 @@
   <ignoredErrors>
     <ignoredError sqref="O7:O45" formulaRange="1"/>
   </ignoredErrors>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13736,109 +13984,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="127" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="128" t="s">
+      <c r="F4" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="102" t="s">
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="102" t="s">
+      <c r="N4" s="123" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="102" t="s">
+      <c r="O4" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="128" t="s">
+      <c r="P4" s="149" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
@@ -13860,17 +14108,17 @@
       <c r="L5" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="M5" s="102"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="128"/>
+      <c r="M5" s="123"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="149"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
       <c r="F6" s="3">
         <v>25</v>
       </c>
@@ -13896,29 +14144,29 @@
         <f>SUM(F6:L6)</f>
         <v>175</v>
       </c>
-      <c r="N6" s="102"/>
-      <c r="O6" s="102"/>
-      <c r="P6" s="128"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="149"/>
     </row>
     <row r="7" spans="1:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="154" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="133"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="133"/>
-      <c r="I7" s="133"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="133"/>
-      <c r="L7" s="133"/>
-      <c r="M7" s="133"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="133"/>
-      <c r="P7" s="133"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="154"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="154"/>
+      <c r="H7" s="154"/>
+      <c r="I7" s="154"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="154"/>
+      <c r="L7" s="154"/>
+      <c r="M7" s="154"/>
+      <c r="N7" s="154"/>
+      <c r="O7" s="154"/>
+      <c r="P7" s="154"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
@@ -14425,24 +14673,24 @@
       <c r="P25" s="4"/>
     </row>
     <row r="26" spans="1:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="A26" s="133" t="s">
+      <c r="A26" s="154" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="133"/>
-      <c r="C26" s="133"/>
-      <c r="D26" s="133"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="133"/>
-      <c r="G26" s="133"/>
-      <c r="H26" s="133"/>
-      <c r="I26" s="133"/>
-      <c r="J26" s="133"/>
-      <c r="K26" s="133"/>
-      <c r="L26" s="133"/>
-      <c r="M26" s="133"/>
-      <c r="N26" s="133"/>
-      <c r="O26" s="133"/>
-      <c r="P26" s="133"/>
+      <c r="B26" s="154"/>
+      <c r="C26" s="154"/>
+      <c r="D26" s="154"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="154"/>
+      <c r="G26" s="154"/>
+      <c r="H26" s="154"/>
+      <c r="I26" s="154"/>
+      <c r="J26" s="154"/>
+      <c r="K26" s="154"/>
+      <c r="L26" s="154"/>
+      <c r="M26" s="154"/>
+      <c r="N26" s="154"/>
+      <c r="O26" s="154"/>
+      <c r="P26" s="154"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
@@ -14927,6 +15175,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14947,34 +15196,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="116"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="130"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="118"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="132"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="133" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="120"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120"/>
-      <c r="E3" s="120"/>
-      <c r="F3" s="121"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="135"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -15157,10 +15406,10 @@
       <c r="F19" s="74"/>
     </row>
     <row r="20" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="108" t="s">
+      <c r="A20" s="141" t="s">
         <v>873</v>
       </c>
-      <c r="B20" s="109"/>
+      <c r="B20" s="142"/>
       <c r="C20" s="75"/>
       <c r="D20" s="75"/>
       <c r="E20" s="75"/>
@@ -15168,44 +15417,44 @@
     </row>
     <row r="21" spans="1:6" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="110" t="s">
+      <c r="A22" s="143" t="s">
         <v>874</v>
       </c>
-      <c r="B22" s="111"/>
+      <c r="B22" s="144"/>
       <c r="C22" s="77"/>
-      <c r="D22" s="123" t="s">
+      <c r="D22" s="137" t="s">
         <v>876</v>
       </c>
-      <c r="E22" s="123"/>
+      <c r="E22" s="137"/>
       <c r="F22" s="72" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="112" t="s">
+      <c r="A23" s="145" t="s">
         <v>875</v>
       </c>
-      <c r="B23" s="113"/>
+      <c r="B23" s="146"/>
       <c r="C23" s="68"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="124"/>
+      <c r="D23" s="138"/>
+      <c r="E23" s="138"/>
       <c r="F23" s="80"/>
     </row>
     <row r="24" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="108" t="s">
+      <c r="A24" s="141" t="s">
         <v>786</v>
       </c>
-      <c r="B24" s="109"/>
+      <c r="B24" s="142"/>
       <c r="C24" s="75"/>
-      <c r="D24" s="125"/>
-      <c r="E24" s="125"/>
+      <c r="D24" s="139"/>
+      <c r="E24" s="139"/>
       <c r="F24" s="76"/>
     </row>
     <row r="26" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="122" t="s">
+      <c r="A26" s="136" t="s">
         <v>877</v>
       </c>
-      <c r="B26" s="122"/>
+      <c r="B26" s="136"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="78"/>
@@ -15216,11 +15465,11 @@
       <c r="F27" s="78"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="107" t="s">
+      <c r="A31" s="140" t="s">
         <v>878</v>
       </c>
-      <c r="B31" s="107"/>
-      <c r="C31" s="107"/>
+      <c r="B31" s="140"/>
+      <c r="C31" s="140"/>
       <c r="D31" s="69"/>
       <c r="E31" s="69"/>
       <c r="F31" s="81" t="s">
@@ -15229,17 +15478,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="D22:E23"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
   </mergeCells>
   <conditionalFormatting sqref="B8:B19">
     <cfRule type="cellIs" dxfId="54" priority="1" operator="equal">
@@ -15272,123 +15521,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="101"/>
-      <c r="T1" s="101"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
     </row>
     <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="101"/>
-      <c r="T2" s="101"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
     </row>
     <row r="3" spans="1:20" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="122" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="101"/>
-      <c r="N3" s="101"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="101"/>
-      <c r="R3" s="101"/>
-      <c r="S3" s="101"/>
-      <c r="T3" s="101"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="122"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="122"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="122"/>
+      <c r="R3" s="122"/>
+      <c r="S3" s="122"/>
+      <c r="T3" s="122"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="128" t="s">
+      <c r="F4" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="128"/>
-      <c r="P4" s="128"/>
-      <c r="Q4" s="128"/>
-      <c r="R4" s="102" t="s">
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="149"/>
+      <c r="O4" s="149"/>
+      <c r="P4" s="149"/>
+      <c r="Q4" s="149"/>
+      <c r="R4" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="S4" s="102" t="s">
+      <c r="S4" s="123" t="s">
         <v>289</v>
       </c>
-      <c r="T4" s="102" t="s">
+      <c r="T4" s="123" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
       <c r="F5" s="2" t="s">
         <v>848</v>
       </c>
@@ -15425,16 +15674,16 @@
       <c r="Q5" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="R5" s="102"/>
-      <c r="S5" s="102"/>
-      <c r="T5" s="102"/>
+      <c r="R5" s="123"/>
+      <c r="S5" s="123"/>
+      <c r="T5" s="123"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
       <c r="F6" s="3" t="s">
         <v>289</v>
       </c>
@@ -15472,32 +15721,32 @@
       <c r="R6" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="S6" s="102"/>
-      <c r="T6" s="102"/>
+      <c r="S6" s="123"/>
+      <c r="T6" s="123"/>
     </row>
     <row r="7" spans="1:20" s="8" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="147" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="126"/>
-      <c r="K7" s="126"/>
-      <c r="L7" s="126"/>
-      <c r="M7" s="126"/>
-      <c r="N7" s="126"/>
-      <c r="O7" s="126"/>
-      <c r="P7" s="126"/>
-      <c r="Q7" s="126"/>
-      <c r="R7" s="126"/>
-      <c r="S7" s="126"/>
-      <c r="T7" s="126"/>
+      <c r="B7" s="147"/>
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="147"/>
+      <c r="K7" s="147"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
+      <c r="R7" s="147"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="147"/>
     </row>
     <row r="8" spans="1:20" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
@@ -17040,28 +17289,28 @@
       </c>
     </row>
     <row r="33" spans="1:20" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="127" t="s">
+      <c r="A33" s="148" t="s">
         <v>165</v>
       </c>
-      <c r="B33" s="127"/>
-      <c r="C33" s="127"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="127"/>
-      <c r="G33" s="127"/>
-      <c r="H33" s="127"/>
-      <c r="I33" s="127"/>
-      <c r="J33" s="127"/>
-      <c r="K33" s="127"/>
-      <c r="L33" s="127"/>
-      <c r="M33" s="127"/>
-      <c r="N33" s="127"/>
-      <c r="O33" s="127"/>
-      <c r="P33" s="127"/>
-      <c r="Q33" s="127"/>
-      <c r="R33" s="127"/>
-      <c r="S33" s="127"/>
-      <c r="T33" s="127"/>
+      <c r="B33" s="148"/>
+      <c r="C33" s="148"/>
+      <c r="D33" s="148"/>
+      <c r="E33" s="148"/>
+      <c r="F33" s="148"/>
+      <c r="G33" s="148"/>
+      <c r="H33" s="148"/>
+      <c r="I33" s="148"/>
+      <c r="J33" s="148"/>
+      <c r="K33" s="148"/>
+      <c r="L33" s="148"/>
+      <c r="M33" s="148"/>
+      <c r="N33" s="148"/>
+      <c r="O33" s="148"/>
+      <c r="P33" s="148"/>
+      <c r="Q33" s="148"/>
+      <c r="R33" s="148"/>
+      <c r="S33" s="148"/>
+      <c r="T33" s="148"/>
     </row>
     <row r="34" spans="1:20" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
@@ -19020,149 +19269,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="101"/>
-      <c r="T1" s="101"/>
-      <c r="U1" s="101"/>
-      <c r="V1" s="101"/>
-      <c r="W1" s="101"/>
-      <c r="X1" s="101"/>
-      <c r="Y1" s="101"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="101"/>
-      <c r="T2" s="101"/>
-      <c r="U2" s="101"/>
-      <c r="V2" s="101"/>
-      <c r="W2" s="101"/>
-      <c r="X2" s="101"/>
-      <c r="Y2" s="101"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
+      <c r="U2" s="122"/>
+      <c r="V2" s="122"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="122"/>
+      <c r="Y2" s="122"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="127" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
-      <c r="R3" s="106"/>
-      <c r="S3" s="106"/>
-      <c r="T3" s="106"/>
-      <c r="U3" s="106"/>
-      <c r="V3" s="106"/>
-      <c r="W3" s="106"/>
-      <c r="X3" s="106"/>
-      <c r="Y3" s="106"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="127"/>
+      <c r="T3" s="127"/>
+      <c r="U3" s="127"/>
+      <c r="V3" s="127"/>
+      <c r="W3" s="127"/>
+      <c r="X3" s="127"/>
+      <c r="Y3" s="127"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="103" t="s">
+      <c r="E4" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="132" t="s">
+      <c r="F4" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="132"/>
-      <c r="H4" s="132"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="132"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="132"/>
-      <c r="R4" s="132"/>
-      <c r="S4" s="132"/>
-      <c r="T4" s="132"/>
-      <c r="U4" s="132"/>
-      <c r="V4" s="132"/>
-      <c r="W4" s="102" t="s">
+      <c r="G4" s="150"/>
+      <c r="H4" s="150"/>
+      <c r="I4" s="150"/>
+      <c r="J4" s="150"/>
+      <c r="K4" s="150"/>
+      <c r="L4" s="150"/>
+      <c r="M4" s="150"/>
+      <c r="N4" s="150"/>
+      <c r="O4" s="150"/>
+      <c r="P4" s="150"/>
+      <c r="Q4" s="150"/>
+      <c r="R4" s="150"/>
+      <c r="S4" s="150"/>
+      <c r="T4" s="150"/>
+      <c r="U4" s="150"/>
+      <c r="V4" s="150"/>
+      <c r="W4" s="123" t="s">
         <v>829</v>
       </c>
-      <c r="X4" s="103" t="s">
+      <c r="X4" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="Y4" s="103" t="s">
+      <c r="Y4" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="102" t="s">
+      <c r="Z4" s="123" t="s">
         <v>786</v>
       </c>
-      <c r="AA4" s="102" t="s">
+      <c r="AA4" s="123" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="67.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="104"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="125"/>
       <c r="F5" s="66" t="s">
         <v>8</v>
       </c>
@@ -19214,18 +19463,18 @@
       <c r="V5" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="W5" s="102"/>
-      <c r="X5" s="104"/>
-      <c r="Y5" s="104"/>
-      <c r="Z5" s="102"/>
-      <c r="AA5" s="102"/>
+      <c r="W5" s="123"/>
+      <c r="X5" s="125"/>
+      <c r="Y5" s="125"/>
+      <c r="Z5" s="123"/>
+      <c r="AA5" s="123"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="105"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="126"/>
       <c r="F6" s="65">
         <v>25</v>
       </c>
@@ -19287,39 +19536,39 @@
       <c r="Y6" s="3" t="s">
         <v>834</v>
       </c>
-      <c r="Z6" s="102"/>
-      <c r="AA6" s="102"/>
+      <c r="Z6" s="123"/>
+      <c r="AA6" s="123"/>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="147" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="126"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="126"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="126"/>
-      <c r="K7" s="126"/>
-      <c r="L7" s="126"/>
-      <c r="M7" s="126"/>
-      <c r="N7" s="126"/>
-      <c r="O7" s="126"/>
-      <c r="P7" s="126"/>
-      <c r="Q7" s="126"/>
-      <c r="R7" s="126"/>
-      <c r="S7" s="126"/>
-      <c r="T7" s="126"/>
-      <c r="U7" s="126"/>
-      <c r="V7" s="126"/>
-      <c r="W7" s="126"/>
-      <c r="X7" s="126"/>
-      <c r="Y7" s="126"/>
-      <c r="Z7" s="126"/>
-      <c r="AA7" s="126"/>
+      <c r="B7" s="147"/>
+      <c r="C7" s="147"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="147"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="147"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="147"/>
+      <c r="K7" s="147"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="147"/>
+      <c r="O7" s="147"/>
+      <c r="P7" s="147"/>
+      <c r="Q7" s="147"/>
+      <c r="R7" s="147"/>
+      <c r="S7" s="147"/>
+      <c r="T7" s="147"/>
+      <c r="U7" s="147"/>
+      <c r="V7" s="147"/>
+      <c r="W7" s="147"/>
+      <c r="X7" s="147"/>
+      <c r="Y7" s="147"/>
+      <c r="Z7" s="147"/>
+      <c r="AA7" s="147"/>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
@@ -21980,35 +22229,35 @@
       </c>
     </row>
     <row r="39" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="129" t="s">
+      <c r="A39" s="151" t="s">
         <v>119</v>
       </c>
-      <c r="B39" s="130"/>
-      <c r="C39" s="130"/>
-      <c r="D39" s="130"/>
-      <c r="E39" s="130"/>
-      <c r="F39" s="130"/>
-      <c r="G39" s="130"/>
-      <c r="H39" s="130"/>
-      <c r="I39" s="130"/>
-      <c r="J39" s="130"/>
-      <c r="K39" s="130"/>
-      <c r="L39" s="130"/>
-      <c r="M39" s="130"/>
-      <c r="N39" s="130"/>
-      <c r="O39" s="130"/>
-      <c r="P39" s="130"/>
-      <c r="Q39" s="130"/>
-      <c r="R39" s="130"/>
-      <c r="S39" s="130"/>
-      <c r="T39" s="130"/>
-      <c r="U39" s="130"/>
-      <c r="V39" s="130"/>
-      <c r="W39" s="130"/>
-      <c r="X39" s="130"/>
-      <c r="Y39" s="130"/>
-      <c r="Z39" s="130"/>
-      <c r="AA39" s="131"/>
+      <c r="B39" s="152"/>
+      <c r="C39" s="152"/>
+      <c r="D39" s="152"/>
+      <c r="E39" s="152"/>
+      <c r="F39" s="152"/>
+      <c r="G39" s="152"/>
+      <c r="H39" s="152"/>
+      <c r="I39" s="152"/>
+      <c r="J39" s="152"/>
+      <c r="K39" s="152"/>
+      <c r="L39" s="152"/>
+      <c r="M39" s="152"/>
+      <c r="N39" s="152"/>
+      <c r="O39" s="152"/>
+      <c r="P39" s="152"/>
+      <c r="Q39" s="152"/>
+      <c r="R39" s="152"/>
+      <c r="S39" s="152"/>
+      <c r="T39" s="152"/>
+      <c r="U39" s="152"/>
+      <c r="V39" s="152"/>
+      <c r="W39" s="152"/>
+      <c r="X39" s="152"/>
+      <c r="Y39" s="152"/>
+      <c r="Z39" s="152"/>
+      <c r="AA39" s="153"/>
     </row>
     <row r="40" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="18">
@@ -23985,6 +24234,11 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="Z4:Z6"/>
+    <mergeCell ref="AA4:AA6"/>
+    <mergeCell ref="A7:AA7"/>
+    <mergeCell ref="A39:AA39"/>
+    <mergeCell ref="Y4:Y5"/>
     <mergeCell ref="A3:Y3"/>
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="A2:Y2"/>
@@ -23996,11 +24250,6 @@
     <mergeCell ref="F4:V4"/>
     <mergeCell ref="W4:W5"/>
     <mergeCell ref="X4:X5"/>
-    <mergeCell ref="Z4:Z6"/>
-    <mergeCell ref="AA4:AA6"/>
-    <mergeCell ref="A7:AA7"/>
-    <mergeCell ref="A39:AA39"/>
-    <mergeCell ref="Y4:Y5"/>
   </mergeCells>
   <conditionalFormatting sqref="F1:V1048576">
     <cfRule type="cellIs" dxfId="51" priority="1" operator="equal">
@@ -24038,155 +24287,155 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="101"/>
-      <c r="T1" s="101"/>
-      <c r="U1" s="101"/>
-      <c r="V1" s="101"/>
-      <c r="W1" s="101"/>
-      <c r="X1" s="101"/>
-      <c r="Y1" s="101"/>
-      <c r="Z1" s="101"/>
-      <c r="AA1" s="101"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
     </row>
     <row r="2" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="101"/>
-      <c r="T2" s="101"/>
-      <c r="U2" s="101"/>
-      <c r="V2" s="101"/>
-      <c r="W2" s="101"/>
-      <c r="X2" s="101"/>
-      <c r="Y2" s="101"/>
-      <c r="Z2" s="101"/>
-      <c r="AA2" s="101"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
+      <c r="U2" s="122"/>
+      <c r="V2" s="122"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="122"/>
+      <c r="Y2" s="122"/>
+      <c r="Z2" s="122"/>
+      <c r="AA2" s="122"/>
     </row>
     <row r="3" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="127" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
-      <c r="R3" s="106"/>
-      <c r="S3" s="106"/>
-      <c r="T3" s="106"/>
-      <c r="U3" s="106"/>
-      <c r="V3" s="106"/>
-      <c r="W3" s="106"/>
-      <c r="X3" s="106"/>
-      <c r="Y3" s="106"/>
-      <c r="Z3" s="106"/>
-      <c r="AA3" s="106"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="127"/>
+      <c r="T3" s="127"/>
+      <c r="U3" s="127"/>
+      <c r="V3" s="127"/>
+      <c r="W3" s="127"/>
+      <c r="X3" s="127"/>
+      <c r="Y3" s="127"/>
+      <c r="Z3" s="127"/>
+      <c r="AA3" s="127"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="103" t="s">
+      <c r="E4" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="132" t="s">
+      <c r="F4" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="132"/>
-      <c r="H4" s="132"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="132"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="132"/>
-      <c r="R4" s="132"/>
-      <c r="S4" s="132"/>
-      <c r="T4" s="132"/>
-      <c r="U4" s="132"/>
-      <c r="V4" s="132"/>
-      <c r="W4" s="102" t="s">
+      <c r="G4" s="150"/>
+      <c r="H4" s="150"/>
+      <c r="I4" s="150"/>
+      <c r="J4" s="150"/>
+      <c r="K4" s="150"/>
+      <c r="L4" s="150"/>
+      <c r="M4" s="150"/>
+      <c r="N4" s="150"/>
+      <c r="O4" s="150"/>
+      <c r="P4" s="150"/>
+      <c r="Q4" s="150"/>
+      <c r="R4" s="150"/>
+      <c r="S4" s="150"/>
+      <c r="T4" s="150"/>
+      <c r="U4" s="150"/>
+      <c r="V4" s="150"/>
+      <c r="W4" s="123" t="s">
         <v>829</v>
       </c>
-      <c r="X4" s="103" t="s">
+      <c r="X4" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="Y4" s="103" t="s">
+      <c r="Y4" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="102" t="s">
+      <c r="Z4" s="123" t="s">
         <v>786</v>
       </c>
-      <c r="AA4" s="102" t="s">
+      <c r="AA4" s="123" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="67.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="104"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="125"/>
       <c r="F5" s="66" t="s">
         <v>8</v>
       </c>
@@ -24238,18 +24487,18 @@
       <c r="V5" s="66" t="s">
         <v>217</v>
       </c>
-      <c r="W5" s="102"/>
-      <c r="X5" s="104"/>
-      <c r="Y5" s="104"/>
-      <c r="Z5" s="102"/>
-      <c r="AA5" s="102"/>
+      <c r="W5" s="123"/>
+      <c r="X5" s="125"/>
+      <c r="Y5" s="125"/>
+      <c r="Z5" s="123"/>
+      <c r="AA5" s="123"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="105"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="126"/>
       <c r="F6" s="65">
         <v>25</v>
       </c>
@@ -24311,39 +24560,39 @@
       <c r="Y6" s="3" t="s">
         <v>834</v>
       </c>
-      <c r="Z6" s="102"/>
-      <c r="AA6" s="102"/>
+      <c r="Z6" s="123"/>
+      <c r="AA6" s="123"/>
     </row>
     <row r="7" spans="1:27" s="8" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="154" t="s">
         <v>119</v>
       </c>
-      <c r="B7" s="133"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="133"/>
-      <c r="I7" s="133"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="133"/>
-      <c r="L7" s="133"/>
-      <c r="M7" s="133"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="133"/>
-      <c r="P7" s="133"/>
-      <c r="Q7" s="133"/>
-      <c r="R7" s="133"/>
-      <c r="S7" s="133"/>
-      <c r="T7" s="133"/>
-      <c r="U7" s="133"/>
-      <c r="V7" s="133"/>
-      <c r="W7" s="133"/>
-      <c r="X7" s="133"/>
-      <c r="Y7" s="133"/>
-      <c r="Z7" s="133"/>
-      <c r="AA7" s="133"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="154"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="154"/>
+      <c r="H7" s="154"/>
+      <c r="I7" s="154"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="154"/>
+      <c r="L7" s="154"/>
+      <c r="M7" s="154"/>
+      <c r="N7" s="154"/>
+      <c r="O7" s="154"/>
+      <c r="P7" s="154"/>
+      <c r="Q7" s="154"/>
+      <c r="R7" s="154"/>
+      <c r="S7" s="154"/>
+      <c r="T7" s="154"/>
+      <c r="U7" s="154"/>
+      <c r="V7" s="154"/>
+      <c r="W7" s="154"/>
+      <c r="X7" s="154"/>
+      <c r="Y7" s="154"/>
+      <c r="Z7" s="154"/>
+      <c r="AA7" s="154"/>
     </row>
     <row r="8" spans="1:27" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
@@ -24595,7 +24844,10 @@
       <c r="Y10" s="16">
         <v>0.84</v>
       </c>
-      <c r="Z10" s="4"/>
+      <c r="Z10" s="4">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
       <c r="AA10" s="4" t="s">
         <v>866</v>
       </c>
@@ -26319,35 +26571,35 @@
       </c>
     </row>
     <row r="31" spans="1:27" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="133" t="s">
+      <c r="A31" s="154" t="s">
         <v>165</v>
       </c>
-      <c r="B31" s="133"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="133"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="133"/>
-      <c r="H31" s="133"/>
-      <c r="I31" s="133"/>
-      <c r="J31" s="133"/>
-      <c r="K31" s="133"/>
-      <c r="L31" s="133"/>
-      <c r="M31" s="133"/>
-      <c r="N31" s="133"/>
-      <c r="O31" s="133"/>
-      <c r="P31" s="133"/>
-      <c r="Q31" s="133"/>
-      <c r="R31" s="133"/>
-      <c r="S31" s="133"/>
-      <c r="T31" s="133"/>
-      <c r="U31" s="133"/>
-      <c r="V31" s="133"/>
-      <c r="W31" s="133"/>
-      <c r="X31" s="133"/>
-      <c r="Y31" s="133"/>
-      <c r="Z31" s="133"/>
-      <c r="AA31" s="133"/>
+      <c r="B31" s="154"/>
+      <c r="C31" s="154"/>
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="154"/>
+      <c r="I31" s="154"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="154"/>
+      <c r="L31" s="154"/>
+      <c r="M31" s="154"/>
+      <c r="N31" s="154"/>
+      <c r="O31" s="154"/>
+      <c r="P31" s="154"/>
+      <c r="Q31" s="154"/>
+      <c r="R31" s="154"/>
+      <c r="S31" s="154"/>
+      <c r="T31" s="154"/>
+      <c r="U31" s="154"/>
+      <c r="V31" s="154"/>
+      <c r="W31" s="154"/>
+      <c r="X31" s="154"/>
+      <c r="Y31" s="154"/>
+      <c r="Z31" s="154"/>
+      <c r="AA31" s="154"/>
     </row>
     <row r="32" spans="1:27" s="8" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
@@ -28461,159 +28713,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="101"/>
-      <c r="T1" s="101"/>
-      <c r="U1" s="101"/>
-      <c r="V1" s="101"/>
-      <c r="W1" s="101"/>
-      <c r="X1" s="101"/>
-      <c r="Y1" s="101"/>
-      <c r="Z1" s="101"/>
-      <c r="AA1" s="101"/>
-      <c r="AB1" s="101"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
+      <c r="Z1" s="122"/>
+      <c r="AA1" s="122"/>
+      <c r="AB1" s="122"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
-      <c r="R2" s="101"/>
-      <c r="S2" s="101"/>
-      <c r="T2" s="101"/>
-      <c r="U2" s="101"/>
-      <c r="V2" s="101"/>
-      <c r="W2" s="101"/>
-      <c r="X2" s="101"/>
-      <c r="Y2" s="101"/>
-      <c r="Z2" s="101"/>
-      <c r="AA2" s="101"/>
-      <c r="AB2" s="101"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
+      <c r="U2" s="122"/>
+      <c r="V2" s="122"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="122"/>
+      <c r="Y2" s="122"/>
+      <c r="Z2" s="122"/>
+      <c r="AA2" s="122"/>
+      <c r="AB2" s="122"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="127" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
-      <c r="R3" s="106"/>
-      <c r="S3" s="106"/>
-      <c r="T3" s="106"/>
-      <c r="U3" s="106"/>
-      <c r="V3" s="106"/>
-      <c r="W3" s="106"/>
-      <c r="X3" s="106"/>
-      <c r="Y3" s="106"/>
-      <c r="Z3" s="106"/>
-      <c r="AA3" s="106"/>
-      <c r="AB3" s="106"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="127"/>
+      <c r="T3" s="127"/>
+      <c r="U3" s="127"/>
+      <c r="V3" s="127"/>
+      <c r="W3" s="127"/>
+      <c r="X3" s="127"/>
+      <c r="Y3" s="127"/>
+      <c r="Z3" s="127"/>
+      <c r="AA3" s="127"/>
+      <c r="AB3" s="127"/>
     </row>
     <row r="4" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="128" t="s">
+      <c r="F4" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="128"/>
-      <c r="P4" s="128"/>
-      <c r="Q4" s="128"/>
-      <c r="R4" s="128"/>
-      <c r="S4" s="128"/>
-      <c r="T4" s="128"/>
-      <c r="U4" s="128"/>
-      <c r="V4" s="128"/>
-      <c r="W4" s="128"/>
-      <c r="X4" s="102" t="s">
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="149"/>
+      <c r="O4" s="149"/>
+      <c r="P4" s="149"/>
+      <c r="Q4" s="149"/>
+      <c r="R4" s="149"/>
+      <c r="S4" s="149"/>
+      <c r="T4" s="149"/>
+      <c r="U4" s="149"/>
+      <c r="V4" s="149"/>
+      <c r="W4" s="149"/>
+      <c r="X4" s="123" t="s">
         <v>14</v>
       </c>
-      <c r="Y4" s="102" t="s">
+      <c r="Y4" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="Z4" s="102" t="s">
+      <c r="Z4" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="AA4" s="103" t="s">
+      <c r="AA4" s="124" t="s">
         <v>786</v>
       </c>
-      <c r="AB4" s="128" t="s">
+      <c r="AB4" s="149" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="79.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
       <c r="F5" s="2" t="s">
         <v>8</v>
       </c>
@@ -28668,18 +28920,18 @@
       <c r="W5" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="X5" s="102"/>
-      <c r="Y5" s="102"/>
-      <c r="Z5" s="102"/>
-      <c r="AA5" s="104"/>
-      <c r="AB5" s="128"/>
+      <c r="X5" s="123"/>
+      <c r="Y5" s="123"/>
+      <c r="Z5" s="123"/>
+      <c r="AA5" s="125"/>
+      <c r="AB5" s="149"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
       <c r="F6" s="3">
         <v>25</v>
       </c>
@@ -28738,42 +28990,42 @@
         <f>SUM(F6:W6)</f>
         <v>525</v>
       </c>
-      <c r="Y6" s="102"/>
-      <c r="Z6" s="102"/>
-      <c r="AA6" s="105"/>
-      <c r="AB6" s="128"/>
+      <c r="Y6" s="123"/>
+      <c r="Z6" s="123"/>
+      <c r="AA6" s="126"/>
+      <c r="AB6" s="149"/>
     </row>
     <row r="7" spans="1:28" ht="21" x14ac:dyDescent="0.35">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="154" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="133"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="133"/>
-      <c r="I7" s="133"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="133"/>
-      <c r="L7" s="133"/>
-      <c r="M7" s="133"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="133"/>
-      <c r="P7" s="133"/>
-      <c r="Q7" s="133"/>
-      <c r="R7" s="133"/>
-      <c r="S7" s="133"/>
-      <c r="T7" s="133"/>
-      <c r="U7" s="133"/>
-      <c r="V7" s="133"/>
-      <c r="W7" s="133"/>
-      <c r="X7" s="133"/>
-      <c r="Y7" s="133"/>
-      <c r="Z7" s="133"/>
-      <c r="AA7" s="133"/>
-      <c r="AB7" s="133"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="154"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="154"/>
+      <c r="H7" s="154"/>
+      <c r="I7" s="154"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="154"/>
+      <c r="L7" s="154"/>
+      <c r="M7" s="154"/>
+      <c r="N7" s="154"/>
+      <c r="O7" s="154"/>
+      <c r="P7" s="154"/>
+      <c r="Q7" s="154"/>
+      <c r="R7" s="154"/>
+      <c r="S7" s="154"/>
+      <c r="T7" s="154"/>
+      <c r="U7" s="154"/>
+      <c r="V7" s="154"/>
+      <c r="W7" s="154"/>
+      <c r="X7" s="154"/>
+      <c r="Y7" s="154"/>
+      <c r="Z7" s="154"/>
+      <c r="AA7" s="154"/>
+      <c r="AB7" s="154"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
@@ -31090,36 +31342,36 @@
       </c>
     </row>
     <row r="34" spans="1:28" ht="21" x14ac:dyDescent="0.35">
-      <c r="A34" s="133" t="s">
+      <c r="A34" s="154" t="s">
         <v>119</v>
       </c>
-      <c r="B34" s="133"/>
-      <c r="C34" s="133"/>
-      <c r="D34" s="133"/>
-      <c r="E34" s="133"/>
-      <c r="F34" s="133"/>
-      <c r="G34" s="133"/>
-      <c r="H34" s="133"/>
-      <c r="I34" s="133"/>
-      <c r="J34" s="133"/>
-      <c r="K34" s="133"/>
-      <c r="L34" s="133"/>
-      <c r="M34" s="133"/>
-      <c r="N34" s="133"/>
-      <c r="O34" s="133"/>
-      <c r="P34" s="133"/>
-      <c r="Q34" s="133"/>
-      <c r="R34" s="133"/>
-      <c r="S34" s="133"/>
-      <c r="T34" s="133"/>
-      <c r="U34" s="133"/>
-      <c r="V34" s="133"/>
-      <c r="W34" s="133"/>
-      <c r="X34" s="133"/>
-      <c r="Y34" s="133"/>
-      <c r="Z34" s="133"/>
-      <c r="AA34" s="133"/>
-      <c r="AB34" s="133"/>
+      <c r="B34" s="154"/>
+      <c r="C34" s="154"/>
+      <c r="D34" s="154"/>
+      <c r="E34" s="154"/>
+      <c r="F34" s="154"/>
+      <c r="G34" s="154"/>
+      <c r="H34" s="154"/>
+      <c r="I34" s="154"/>
+      <c r="J34" s="154"/>
+      <c r="K34" s="154"/>
+      <c r="L34" s="154"/>
+      <c r="M34" s="154"/>
+      <c r="N34" s="154"/>
+      <c r="O34" s="154"/>
+      <c r="P34" s="154"/>
+      <c r="Q34" s="154"/>
+      <c r="R34" s="154"/>
+      <c r="S34" s="154"/>
+      <c r="T34" s="154"/>
+      <c r="U34" s="154"/>
+      <c r="V34" s="154"/>
+      <c r="W34" s="154"/>
+      <c r="X34" s="154"/>
+      <c r="Y34" s="154"/>
+      <c r="Z34" s="154"/>
+      <c r="AA34" s="154"/>
+      <c r="AB34" s="154"/>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
@@ -33324,113 +33576,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="127" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
     </row>
     <row r="4" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="128" t="s">
+      <c r="F4" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="103" t="s">
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="103" t="s">
+      <c r="O4" s="124" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="103" t="s">
+      <c r="P4" s="124" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="137" t="s">
+      <c r="Q4" s="158" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="43.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
@@ -33455,17 +33707,17 @@
       <c r="M5" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="N5" s="105"/>
-      <c r="O5" s="104"/>
-      <c r="P5" s="104"/>
-      <c r="Q5" s="138"/>
+      <c r="N5" s="126"/>
+      <c r="O5" s="125"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="159"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
       <c r="F6" s="3">
         <v>100</v>
       </c>
@@ -33494,30 +33746,30 @@
         <f>SUM(F6:M6)</f>
         <v>800</v>
       </c>
-      <c r="O6" s="105"/>
-      <c r="P6" s="105"/>
-      <c r="Q6" s="139"/>
+      <c r="O6" s="126"/>
+      <c r="P6" s="126"/>
+      <c r="Q6" s="160"/>
     </row>
     <row r="7" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="155" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="135"/>
-      <c r="C7" s="135"/>
-      <c r="D7" s="135"/>
-      <c r="E7" s="135"/>
-      <c r="F7" s="135"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="135"/>
-      <c r="I7" s="135"/>
-      <c r="J7" s="135"/>
-      <c r="K7" s="135"/>
-      <c r="L7" s="135"/>
-      <c r="M7" s="135"/>
-      <c r="N7" s="135"/>
-      <c r="O7" s="135"/>
-      <c r="P7" s="135"/>
-      <c r="Q7" s="136"/>
+      <c r="B7" s="156"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="156"/>
+      <c r="H7" s="156"/>
+      <c r="I7" s="156"/>
+      <c r="J7" s="156"/>
+      <c r="K7" s="156"/>
+      <c r="L7" s="156"/>
+      <c r="M7" s="156"/>
+      <c r="N7" s="156"/>
+      <c r="O7" s="156"/>
+      <c r="P7" s="156"/>
+      <c r="Q7" s="157"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
@@ -34620,25 +34872,25 @@
       </c>
     </row>
     <row r="28" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A28" s="133" t="s">
+      <c r="A28" s="154" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="133"/>
-      <c r="C28" s="133"/>
-      <c r="D28" s="133"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="133"/>
-      <c r="G28" s="133"/>
-      <c r="H28" s="133"/>
-      <c r="I28" s="133"/>
-      <c r="J28" s="133"/>
-      <c r="K28" s="133"/>
-      <c r="L28" s="133"/>
-      <c r="M28" s="133"/>
-      <c r="N28" s="133"/>
-      <c r="O28" s="133"/>
-      <c r="P28" s="133"/>
-      <c r="Q28" s="133"/>
+      <c r="B28" s="154"/>
+      <c r="C28" s="154"/>
+      <c r="D28" s="154"/>
+      <c r="E28" s="154"/>
+      <c r="F28" s="154"/>
+      <c r="G28" s="154"/>
+      <c r="H28" s="154"/>
+      <c r="I28" s="154"/>
+      <c r="J28" s="154"/>
+      <c r="K28" s="154"/>
+      <c r="L28" s="154"/>
+      <c r="M28" s="154"/>
+      <c r="N28" s="154"/>
+      <c r="O28" s="154"/>
+      <c r="P28" s="154"/>
+      <c r="Q28" s="154"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
@@ -36394,113 +36646,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="127" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="128" t="s">
+      <c r="F4" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="102" t="s">
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
+      <c r="N4" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="102" t="s">
+      <c r="O4" s="123" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="102" t="s">
+      <c r="P4" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="128" t="s">
+      <c r="Q4" s="149" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="43.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
       <c r="F5" s="2" t="s">
         <v>217</v>
       </c>
@@ -36525,17 +36777,17 @@
       <c r="M5" s="2" t="s">
         <v>802</v>
       </c>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="128"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="149"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
       <c r="F6" s="3">
         <v>100</v>
       </c>
@@ -36564,30 +36816,30 @@
         <f>SUM(F6:M6)</f>
         <v>800</v>
       </c>
-      <c r="O6" s="102"/>
-      <c r="P6" s="102"/>
-      <c r="Q6" s="128"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="123"/>
+      <c r="Q6" s="149"/>
     </row>
     <row r="7" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="154" t="s">
         <v>165</v>
       </c>
-      <c r="B7" s="133"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="G7" s="133"/>
-      <c r="H7" s="133"/>
-      <c r="I7" s="133"/>
-      <c r="J7" s="133"/>
-      <c r="K7" s="133"/>
-      <c r="L7" s="133"/>
-      <c r="M7" s="133"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="133"/>
-      <c r="P7" s="133"/>
-      <c r="Q7" s="133"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="154"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="154"/>
+      <c r="H7" s="154"/>
+      <c r="I7" s="154"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="154"/>
+      <c r="L7" s="154"/>
+      <c r="M7" s="154"/>
+      <c r="N7" s="154"/>
+      <c r="O7" s="154"/>
+      <c r="P7" s="154"/>
+      <c r="Q7" s="154"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
@@ -36640,7 +36892,9 @@
         <f>O8/N8</f>
         <v>0.71499999999999997</v>
       </c>
-      <c r="Q8" s="4"/>
+      <c r="Q8" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
@@ -36693,7 +36947,9 @@
         <f t="shared" ref="P9:P54" si="1">O9/N9</f>
         <v>0.67625000000000002</v>
       </c>
-      <c r="Q9" s="4"/>
+      <c r="Q9" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
@@ -36746,7 +37002,9 @@
         <f t="shared" si="1"/>
         <v>0.17125000000000001</v>
       </c>
-      <c r="Q10" s="4"/>
+      <c r="Q10" s="4" t="s">
+        <v>937</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
@@ -36799,7 +37057,9 @@
         <f t="shared" si="1"/>
         <v>0.68</v>
       </c>
-      <c r="Q11" s="4"/>
+      <c r="Q11" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
@@ -36852,7 +37112,9 @@
         <f t="shared" si="1"/>
         <v>0.45250000000000001</v>
       </c>
-      <c r="Q12" s="4"/>
+      <c r="Q12" s="4" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
@@ -36905,7 +37167,9 @@
         <f t="shared" si="1"/>
         <v>0.48</v>
       </c>
-      <c r="Q13" s="4"/>
+      <c r="Q13" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
@@ -36958,7 +37222,9 @@
         <f t="shared" si="1"/>
         <v>0.44</v>
       </c>
-      <c r="Q14" s="4"/>
+      <c r="Q14" s="4" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
@@ -37011,7 +37277,9 @@
         <f t="shared" si="1"/>
         <v>0.24249999999999999</v>
       </c>
-      <c r="Q15" s="4"/>
+      <c r="Q15" s="4" t="s">
+        <v>937</v>
+      </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
@@ -37064,7 +37332,9 @@
         <f t="shared" si="1"/>
         <v>0.50875000000000004</v>
       </c>
-      <c r="Q16" s="4"/>
+      <c r="Q16" s="4" t="s">
+        <v>934</v>
+      </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
@@ -37117,7 +37387,9 @@
         <f t="shared" si="1"/>
         <v>0.94750000000000001</v>
       </c>
-      <c r="Q17" s="4"/>
+      <c r="Q17" s="4" t="s">
+        <v>899</v>
+      </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
@@ -37170,7 +37442,9 @@
         <f t="shared" si="1"/>
         <v>0.71250000000000002</v>
       </c>
-      <c r="Q18" s="4"/>
+      <c r="Q18" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
@@ -37223,7 +37497,9 @@
         <f t="shared" si="1"/>
         <v>0.41625000000000001</v>
       </c>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="4" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
@@ -37276,7 +37552,9 @@
         <f t="shared" si="1"/>
         <v>0.78500000000000003</v>
       </c>
-      <c r="Q20" s="4"/>
+      <c r="Q20" s="4" t="s">
+        <v>914</v>
+      </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
@@ -37329,7 +37607,9 @@
         <f t="shared" si="1"/>
         <v>0.53374999999999995</v>
       </c>
-      <c r="Q21" s="4"/>
+      <c r="Q21" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
@@ -37382,7 +37662,9 @@
         <f t="shared" si="1"/>
         <v>0.52625</v>
       </c>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
@@ -37435,7 +37717,9 @@
         <f t="shared" si="1"/>
         <v>0.90749999999999997</v>
       </c>
-      <c r="Q23" s="4"/>
+      <c r="Q23" s="4" t="s">
+        <v>911</v>
+      </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
@@ -37488,7 +37772,9 @@
         <f t="shared" si="1"/>
         <v>0.60624999999999996</v>
       </c>
-      <c r="Q24" s="4"/>
+      <c r="Q24" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
@@ -37541,7 +37827,9 @@
         <f t="shared" si="1"/>
         <v>0.79125000000000001</v>
       </c>
-      <c r="Q25" s="4"/>
+      <c r="Q25" s="4" t="s">
+        <v>900</v>
+      </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
@@ -37594,7 +37882,9 @@
         <f t="shared" si="1"/>
         <v>0.67374999999999996</v>
       </c>
-      <c r="Q26" s="4"/>
+      <c r="Q26" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
@@ -37647,7 +37937,9 @@
         <f t="shared" si="1"/>
         <v>0.81</v>
       </c>
-      <c r="Q27" s="4"/>
+      <c r="Q27" s="4" t="s">
+        <v>915</v>
+      </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
@@ -37700,7 +37992,9 @@
         <f t="shared" si="1"/>
         <v>0.65625</v>
       </c>
-      <c r="Q28" s="4"/>
+      <c r="Q28" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
@@ -37753,7 +38047,9 @@
         <f t="shared" si="1"/>
         <v>0.88500000000000001</v>
       </c>
-      <c r="Q29" s="4"/>
+      <c r="Q29" s="4" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
@@ -37806,28 +38102,30 @@
         <f t="shared" si="1"/>
         <v>0.54749999999999999</v>
       </c>
-      <c r="Q30" s="4"/>
+      <c r="Q30" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="31" spans="1:17" ht="21" x14ac:dyDescent="0.35">
-      <c r="A31" s="133" t="s">
+      <c r="A31" s="154" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="133"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="133"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="133"/>
-      <c r="H31" s="133"/>
-      <c r="I31" s="133"/>
-      <c r="J31" s="133"/>
-      <c r="K31" s="133"/>
-      <c r="L31" s="133"/>
-      <c r="M31" s="133"/>
-      <c r="N31" s="133"/>
-      <c r="O31" s="133"/>
-      <c r="P31" s="133"/>
-      <c r="Q31" s="133"/>
+      <c r="B31" s="154"/>
+      <c r="C31" s="154"/>
+      <c r="D31" s="154"/>
+      <c r="E31" s="154"/>
+      <c r="F31" s="154"/>
+      <c r="G31" s="154"/>
+      <c r="H31" s="154"/>
+      <c r="I31" s="154"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="154"/>
+      <c r="L31" s="154"/>
+      <c r="M31" s="154"/>
+      <c r="N31" s="154"/>
+      <c r="O31" s="154"/>
+      <c r="P31" s="154"/>
+      <c r="Q31" s="154"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
@@ -37880,7 +38178,9 @@
         <f t="shared" si="1"/>
         <v>0.39624999999999999</v>
       </c>
-      <c r="Q32" s="4"/>
+      <c r="Q32" s="4" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
@@ -37933,7 +38233,9 @@
         <f t="shared" si="1"/>
         <v>0.57125000000000004</v>
       </c>
-      <c r="Q33" s="4"/>
+      <c r="Q33" s="4" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
@@ -37986,7 +38288,9 @@
         <f t="shared" si="1"/>
         <v>0.76749999999999996</v>
       </c>
-      <c r="Q34" s="4"/>
+      <c r="Q34" s="4" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
@@ -38039,7 +38343,9 @@
         <f t="shared" si="1"/>
         <v>0.52875000000000005</v>
       </c>
-      <c r="Q35" s="4"/>
+      <c r="Q35" s="4" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
@@ -38092,7 +38398,9 @@
         <f t="shared" si="1"/>
         <v>0.83499999999999996</v>
       </c>
-      <c r="Q36" s="4"/>
+      <c r="Q36" s="4" t="s">
+        <v>893</v>
+      </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
@@ -38145,7 +38453,9 @@
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="Q37" s="4"/>
+      <c r="Q37" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
@@ -38198,7 +38508,9 @@
         <f t="shared" si="1"/>
         <v>0.42749999999999999</v>
       </c>
-      <c r="Q38" s="4"/>
+      <c r="Q38" s="4" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
@@ -38251,7 +38563,9 @@
         <f t="shared" si="1"/>
         <v>0.25624999999999998</v>
       </c>
-      <c r="Q39" s="4"/>
+      <c r="Q39" s="4" t="s">
+        <v>937</v>
+      </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
@@ -38304,7 +38618,9 @@
         <f t="shared" si="1"/>
         <v>0.77249999999999996</v>
       </c>
-      <c r="Q40" s="4"/>
+      <c r="Q40" s="4" t="s">
+        <v>889</v>
+      </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
@@ -38357,7 +38673,9 @@
         <f t="shared" si="1"/>
         <v>0.73499999999999999</v>
       </c>
-      <c r="Q41" s="4"/>
+      <c r="Q41" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
@@ -38410,7 +38728,9 @@
         <f t="shared" si="1"/>
         <v>0.78374999999999995</v>
       </c>
-      <c r="Q42" s="4"/>
+      <c r="Q42" s="4" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
@@ -38463,7 +38783,9 @@
         <f t="shared" si="1"/>
         <v>0.65125</v>
       </c>
-      <c r="Q43" s="4"/>
+      <c r="Q43" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
@@ -38516,7 +38838,9 @@
         <f t="shared" si="1"/>
         <v>0.89375000000000004</v>
       </c>
-      <c r="Q44" s="4"/>
+      <c r="Q44" s="4" t="s">
+        <v>908</v>
+      </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
@@ -38569,7 +38893,9 @@
         <f t="shared" si="1"/>
         <v>0.39874999999999999</v>
       </c>
-      <c r="Q45" s="4"/>
+      <c r="Q45" s="4" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
@@ -38622,7 +38948,9 @@
         <f t="shared" si="1"/>
         <v>0.8175</v>
       </c>
-      <c r="Q46" s="4"/>
+      <c r="Q46" s="4" t="s">
+        <v>905</v>
+      </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
@@ -38675,7 +39003,9 @@
         <f t="shared" si="1"/>
         <v>0.63500000000000001</v>
       </c>
-      <c r="Q47" s="4"/>
+      <c r="Q47" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
@@ -38728,7 +39058,9 @@
         <f t="shared" si="1"/>
         <v>0.41499999999999998</v>
       </c>
-      <c r="Q48" s="4"/>
+      <c r="Q48" s="4" t="s">
+        <v>892</v>
+      </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
@@ -38781,7 +39113,9 @@
         <f t="shared" si="1"/>
         <v>0.89375000000000004</v>
       </c>
-      <c r="Q49" s="4"/>
+      <c r="Q49" s="4" t="s">
+        <v>908</v>
+      </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
@@ -38834,7 +39168,9 @@
         <f t="shared" si="1"/>
         <v>0.69625000000000004</v>
       </c>
-      <c r="Q50" s="4"/>
+      <c r="Q50" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
@@ -38887,7 +39223,9 @@
         <f t="shared" si="1"/>
         <v>0.63375000000000004</v>
       </c>
-      <c r="Q51" s="4"/>
+      <c r="Q51" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
@@ -38940,7 +39278,9 @@
         <f t="shared" si="1"/>
         <v>0.56125000000000003</v>
       </c>
-      <c r="Q52" s="4"/>
+      <c r="Q52" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
@@ -38993,7 +39333,9 @@
         <f t="shared" si="1"/>
         <v>0.67500000000000004</v>
       </c>
-      <c r="Q53" s="4"/>
+      <c r="Q53" s="4" t="s">
+        <v>936</v>
+      </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
@@ -39046,7 +39388,9 @@
         <f t="shared" si="1"/>
         <v>0.41749999999999998</v>
       </c>
-      <c r="Q54" s="4"/>
+      <c r="Q54" s="4" t="s">
+        <v>892</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -39106,113 +39450,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="122" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="127" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="106"/>
-      <c r="C3" s="106"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="106"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="106"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="106"/>
-      <c r="J3" s="106"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="106"/>
-      <c r="Q3" s="106"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="127"/>
+      <c r="J3" s="127"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="C4" s="123" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="144" t="s">
+      <c r="F4" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="145"/>
-      <c r="M4" s="146"/>
-      <c r="N4" s="102" t="s">
+      <c r="G4" s="162"/>
+      <c r="H4" s="162"/>
+      <c r="I4" s="162"/>
+      <c r="J4" s="162"/>
+      <c r="K4" s="162"/>
+      <c r="L4" s="162"/>
+      <c r="M4" s="163"/>
+      <c r="N4" s="123" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="102" t="s">
+      <c r="O4" s="123" t="s">
         <v>14</v>
       </c>
-      <c r="P4" s="102" t="s">
+      <c r="P4" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="Q4" s="128" t="s">
+      <c r="Q4" s="149" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="43.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="A5" s="123"/>
+      <c r="B5" s="123"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="123"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
@@ -39237,17 +39581,17 @@
       <c r="M5" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="N5" s="102"/>
-      <c r="O5" s="102"/>
-      <c r="P5" s="102"/>
-      <c r="Q5" s="128"/>
+      <c r="N5" s="123"/>
+      <c r="O5" s="123"/>
+      <c r="P5" s="123"/>
+      <c r="Q5" s="149"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="A6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="123"/>
       <c r="F6" s="3">
         <v>100</v>
       </c>
@@ -39276,9 +39620,9 @@
         <f>SUM(F6:M6)</f>
         <v>800</v>
       </c>
-      <c r="O6" s="102"/>
-      <c r="P6" s="102"/>
-      <c r="Q6" s="128"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="123"/>
+      <c r="Q6" s="149"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="49">
@@ -39327,7 +39671,7 @@
         <f>SUM(F7:M7)</f>
         <v>375</v>
       </c>
-      <c r="P7" s="149">
+      <c r="P7" s="104">
         <f>O7/N7</f>
         <v>0.46875</v>
       </c>
@@ -39351,25 +39695,25 @@
       <c r="E8" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F8" s="147">
+      <c r="F8" s="102">
         <v>33</v>
       </c>
-      <c r="G8" s="147">
+      <c r="G8" s="102">
         <v>35</v>
       </c>
-      <c r="H8" s="147">
+      <c r="H8" s="102">
         <v>76</v>
       </c>
-      <c r="I8" s="147">
+      <c r="I8" s="102">
         <v>58</v>
       </c>
-      <c r="J8" s="147">
+      <c r="J8" s="102">
         <v>33</v>
       </c>
-      <c r="K8" s="147">
+      <c r="K8" s="102">
         <v>40</v>
       </c>
-      <c r="L8" s="147">
+      <c r="L8" s="102">
         <v>60</v>
       </c>
       <c r="M8" s="67">
@@ -39382,7 +39726,7 @@
         <f t="shared" ref="O8:O48" si="0">SUM(F8:M8)</f>
         <v>389</v>
       </c>
-      <c r="P8" s="149">
+      <c r="P8" s="104">
         <f t="shared" ref="P8:P48" si="1">O8/N8</f>
         <v>0.48625000000000002</v>
       </c>
@@ -39391,7 +39735,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="140">
+      <c r="A9" s="98">
         <v>3</v>
       </c>
       <c r="B9" s="29">
@@ -39437,7 +39781,7 @@
         <f t="shared" si="0"/>
         <v>475</v>
       </c>
-      <c r="P9" s="149">
+      <c r="P9" s="104">
         <f t="shared" si="1"/>
         <v>0.59375</v>
       </c>
@@ -39492,7 +39836,7 @@
         <f t="shared" si="0"/>
         <v>493</v>
       </c>
-      <c r="P10" s="149">
+      <c r="P10" s="104">
         <f t="shared" si="1"/>
         <v>0.61624999999999996</v>
       </c>
@@ -39501,7 +39845,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="140">
+      <c r="A11" s="98">
         <v>5</v>
       </c>
       <c r="B11" s="26">
@@ -39547,7 +39891,7 @@
         <f t="shared" si="0"/>
         <v>165</v>
       </c>
-      <c r="P11" s="149">
+      <c r="P11" s="104">
         <f t="shared" si="1"/>
         <v>0.20624999999999999</v>
       </c>
@@ -39556,7 +39900,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="140">
+      <c r="A12" s="98">
         <v>6</v>
       </c>
       <c r="B12" s="29">
@@ -39602,7 +39946,7 @@
         <f t="shared" si="0"/>
         <v>435</v>
       </c>
-      <c r="P12" s="149">
+      <c r="P12" s="104">
         <f t="shared" si="1"/>
         <v>0.54374999999999996</v>
       </c>
@@ -39611,7 +39955,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="140">
+      <c r="A13" s="98">
         <v>7</v>
       </c>
       <c r="B13" s="29">
@@ -39657,7 +40001,7 @@
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
-      <c r="P13" s="149">
+      <c r="P13" s="104">
         <f t="shared" si="1"/>
         <v>0.20499999999999999</v>
       </c>
@@ -39712,7 +40056,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P14" s="149">
+      <c r="P14" s="104">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -39767,7 +40111,7 @@
         <f t="shared" si="0"/>
         <v>672</v>
       </c>
-      <c r="P15" s="149">
+      <c r="P15" s="104">
         <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
@@ -39791,25 +40135,25 @@
       <c r="E16" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F16" s="147">
+      <c r="F16" s="102">
         <v>33</v>
       </c>
-      <c r="G16" s="147">
+      <c r="G16" s="102">
         <v>33</v>
       </c>
-      <c r="H16" s="147">
+      <c r="H16" s="102">
         <v>42</v>
       </c>
-      <c r="I16" s="147">
+      <c r="I16" s="102">
         <v>59</v>
       </c>
-      <c r="J16" s="147">
+      <c r="J16" s="102">
         <v>33</v>
       </c>
-      <c r="K16" s="147">
+      <c r="K16" s="102">
         <v>33</v>
       </c>
-      <c r="L16" s="147">
+      <c r="L16" s="102">
         <v>93</v>
       </c>
       <c r="M16" s="67">
@@ -39822,7 +40166,7 @@
         <f t="shared" si="0"/>
         <v>361</v>
       </c>
-      <c r="P16" s="149">
+      <c r="P16" s="104">
         <f t="shared" si="1"/>
         <v>0.45124999999999998</v>
       </c>
@@ -39877,7 +40221,7 @@
         <f t="shared" si="0"/>
         <v>349</v>
       </c>
-      <c r="P17" s="149">
+      <c r="P17" s="104">
         <f t="shared" si="1"/>
         <v>0.43625000000000003</v>
       </c>
@@ -39932,7 +40276,7 @@
         <f t="shared" si="0"/>
         <v>402</v>
       </c>
-      <c r="P18" s="149">
+      <c r="P18" s="104">
         <f t="shared" si="1"/>
         <v>0.50249999999999995</v>
       </c>
@@ -39987,7 +40331,7 @@
         <f t="shared" si="0"/>
         <v>422</v>
       </c>
-      <c r="P19" s="149">
+      <c r="P19" s="104">
         <f t="shared" si="1"/>
         <v>0.52749999999999997</v>
       </c>
@@ -40011,25 +40355,25 @@
       <c r="E20" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F20" s="147">
+      <c r="F20" s="102">
         <v>0</v>
       </c>
-      <c r="G20" s="147">
+      <c r="G20" s="102">
         <v>10</v>
       </c>
-      <c r="H20" s="147">
+      <c r="H20" s="102">
         <v>7</v>
       </c>
-      <c r="I20" s="147">
+      <c r="I20" s="102">
         <v>4</v>
       </c>
-      <c r="J20" s="147">
-        <v>5</v>
-      </c>
-      <c r="K20" s="147">
+      <c r="J20" s="102">
+        <v>5</v>
+      </c>
+      <c r="K20" s="102">
         <v>3</v>
       </c>
-      <c r="L20" s="147">
+      <c r="L20" s="102">
         <v>11</v>
       </c>
       <c r="M20" s="67">
@@ -40042,7 +40386,7 @@
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="P20" s="149">
+      <c r="P20" s="104">
         <f t="shared" si="1"/>
         <v>9.7500000000000003E-2</v>
       </c>
@@ -40066,25 +40410,25 @@
       <c r="E21" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F21" s="147">
+      <c r="F21" s="102">
         <v>33</v>
       </c>
-      <c r="G21" s="147">
+      <c r="G21" s="102">
         <v>46</v>
       </c>
-      <c r="H21" s="147">
+      <c r="H21" s="102">
         <v>44</v>
       </c>
-      <c r="I21" s="147">
+      <c r="I21" s="102">
         <v>34</v>
       </c>
-      <c r="J21" s="147">
+      <c r="J21" s="102">
         <v>33</v>
       </c>
-      <c r="K21" s="147">
+      <c r="K21" s="102">
         <v>33</v>
       </c>
-      <c r="L21" s="147">
+      <c r="L21" s="102">
         <v>33</v>
       </c>
       <c r="M21" s="67">
@@ -40097,7 +40441,7 @@
         <f t="shared" si="0"/>
         <v>308</v>
       </c>
-      <c r="P21" s="149">
+      <c r="P21" s="104">
         <f t="shared" si="1"/>
         <v>0.38500000000000001</v>
       </c>
@@ -40121,25 +40465,25 @@
       <c r="E22" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F22" s="147">
+      <c r="F22" s="102">
         <v>80</v>
       </c>
-      <c r="G22" s="147">
+      <c r="G22" s="102">
         <v>33</v>
       </c>
-      <c r="H22" s="147">
+      <c r="H22" s="102">
         <v>56</v>
       </c>
-      <c r="I22" s="147">
+      <c r="I22" s="102">
         <v>34</v>
       </c>
-      <c r="J22" s="147">
+      <c r="J22" s="102">
         <v>33</v>
       </c>
-      <c r="K22" s="147">
+      <c r="K22" s="102">
         <v>48</v>
       </c>
-      <c r="L22" s="147">
+      <c r="L22" s="102">
         <v>72</v>
       </c>
       <c r="M22" s="67">
@@ -40152,7 +40496,7 @@
         <f t="shared" si="0"/>
         <v>398</v>
       </c>
-      <c r="P22" s="149">
+      <c r="P22" s="104">
         <f t="shared" si="1"/>
         <v>0.4975</v>
       </c>
@@ -40207,7 +40551,7 @@
         <f t="shared" si="0"/>
         <v>168</v>
       </c>
-      <c r="P23" s="149">
+      <c r="P23" s="104">
         <f t="shared" si="1"/>
         <v>0.21</v>
       </c>
@@ -40217,7 +40561,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="49">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B24" s="29">
         <v>436</v>
@@ -40262,7 +40606,7 @@
         <f t="shared" si="0"/>
         <v>405</v>
       </c>
-      <c r="P24" s="149">
+      <c r="P24" s="104">
         <f t="shared" si="1"/>
         <v>0.50624999999999998</v>
       </c>
@@ -40272,7 +40616,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="49">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B25" s="29">
         <v>443</v>
@@ -40317,7 +40661,7 @@
         <f t="shared" si="0"/>
         <v>640</v>
       </c>
-      <c r="P25" s="149">
+      <c r="P25" s="104">
         <f t="shared" si="1"/>
         <v>0.8</v>
       </c>
@@ -40327,7 +40671,7 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="49">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B26" s="29">
         <v>348</v>
@@ -40372,7 +40716,7 @@
         <f t="shared" si="0"/>
         <v>629</v>
       </c>
-      <c r="P26" s="149">
+      <c r="P26" s="104">
         <f t="shared" si="1"/>
         <v>0.78625</v>
       </c>
@@ -40382,7 +40726,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="49">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B27" s="29">
         <v>619</v>
@@ -40427,7 +40771,7 @@
         <f t="shared" si="0"/>
         <v>626</v>
       </c>
-      <c r="P27" s="149">
+      <c r="P27" s="104">
         <f t="shared" si="1"/>
         <v>0.78249999999999997</v>
       </c>
@@ -40437,7 +40781,7 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B28" s="29">
         <v>442</v>
@@ -40482,7 +40826,7 @@
         <f t="shared" si="0"/>
         <v>548</v>
       </c>
-      <c r="P28" s="149">
+      <c r="P28" s="104">
         <f t="shared" si="1"/>
         <v>0.68500000000000005</v>
       </c>
@@ -40492,7 +40836,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="49">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B29" s="29">
         <v>618</v>
@@ -40506,25 +40850,25 @@
       <c r="E29" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F29" s="148">
+      <c r="F29" s="103">
         <v>61</v>
       </c>
-      <c r="G29" s="148">
+      <c r="G29" s="103">
         <v>56</v>
       </c>
-      <c r="H29" s="148">
+      <c r="H29" s="103">
         <v>86</v>
       </c>
-      <c r="I29" s="148">
+      <c r="I29" s="103">
         <v>57</v>
       </c>
-      <c r="J29" s="148">
+      <c r="J29" s="103">
         <v>53</v>
       </c>
-      <c r="K29" s="148">
+      <c r="K29" s="103">
         <v>42</v>
       </c>
-      <c r="L29" s="148">
+      <c r="L29" s="103">
         <v>91</v>
       </c>
       <c r="M29" s="67">
@@ -40537,7 +40881,7 @@
         <f t="shared" si="0"/>
         <v>530</v>
       </c>
-      <c r="P29" s="149">
+      <c r="P29" s="104">
         <f t="shared" si="1"/>
         <v>0.66249999999999998</v>
       </c>
@@ -40547,7 +40891,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="49">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B30" s="29">
         <v>633</v>
@@ -40592,7 +40936,7 @@
         <f t="shared" si="0"/>
         <v>574</v>
       </c>
-      <c r="P30" s="149">
+      <c r="P30" s="104">
         <f t="shared" si="1"/>
         <v>0.71750000000000003</v>
       </c>
@@ -40602,7 +40946,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="49">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B31" s="29">
         <v>614</v>
@@ -40647,7 +40991,7 @@
         <f t="shared" si="0"/>
         <v>686</v>
       </c>
-      <c r="P31" s="149">
+      <c r="P31" s="104">
         <f t="shared" si="1"/>
         <v>0.85750000000000004</v>
       </c>
@@ -40656,8 +41000,8 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="141">
-        <v>26</v>
+      <c r="A32" s="49">
+        <v>9</v>
       </c>
       <c r="B32" s="29">
         <v>778</v>
@@ -40671,25 +41015,25 @@
       <c r="E32" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F32" s="148">
+      <c r="F32" s="103">
         <v>64</v>
       </c>
-      <c r="G32" s="148">
+      <c r="G32" s="103">
         <v>55</v>
       </c>
-      <c r="H32" s="148">
+      <c r="H32" s="103">
         <v>88</v>
       </c>
-      <c r="I32" s="148">
+      <c r="I32" s="103">
         <v>68</v>
       </c>
-      <c r="J32" s="148">
+      <c r="J32" s="103">
         <v>55</v>
       </c>
-      <c r="K32" s="148">
+      <c r="K32" s="103">
         <v>72</v>
       </c>
-      <c r="L32" s="148">
+      <c r="L32" s="103">
         <v>93</v>
       </c>
       <c r="M32" s="67">
@@ -40702,7 +41046,7 @@
         <f t="shared" si="0"/>
         <v>579</v>
       </c>
-      <c r="P32" s="149">
+      <c r="P32" s="104">
         <f t="shared" si="1"/>
         <v>0.72375</v>
       </c>
@@ -40711,8 +41055,8 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="141">
-        <v>27</v>
+      <c r="A33" s="49">
+        <v>10</v>
       </c>
       <c r="B33" s="29">
         <v>379</v>
@@ -40757,7 +41101,7 @@
         <f t="shared" si="0"/>
         <v>579</v>
       </c>
-      <c r="P33" s="149">
+      <c r="P33" s="104">
         <f t="shared" si="1"/>
         <v>0.72375</v>
       </c>
@@ -40767,7 +41111,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="49">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B34" s="29">
         <v>566</v>
@@ -40812,7 +41156,7 @@
         <f t="shared" si="0"/>
         <v>533</v>
       </c>
-      <c r="P34" s="149">
+      <c r="P34" s="104">
         <f t="shared" si="1"/>
         <v>0.66625000000000001</v>
       </c>
@@ -40821,8 +41165,8 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="52">
-        <v>29</v>
+      <c r="A35" s="49">
+        <v>12</v>
       </c>
       <c r="B35" s="29">
         <v>716</v>
@@ -40867,7 +41211,7 @@
         <f t="shared" si="0"/>
         <v>346</v>
       </c>
-      <c r="P35" s="149">
+      <c r="P35" s="104">
         <f t="shared" si="1"/>
         <v>0.4325</v>
       </c>
@@ -40876,8 +41220,8 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="141">
-        <v>30</v>
+      <c r="A36" s="49">
+        <v>13</v>
       </c>
       <c r="B36" s="29">
         <v>769</v>
@@ -40891,25 +41235,25 @@
       <c r="E36" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F36" s="148">
+      <c r="F36" s="103">
         <v>33</v>
       </c>
-      <c r="G36" s="148">
+      <c r="G36" s="103">
         <v>26</v>
       </c>
-      <c r="H36" s="148">
+      <c r="H36" s="103">
         <v>55</v>
       </c>
-      <c r="I36" s="148" t="s">
-        <v>807</v>
-      </c>
-      <c r="J36" s="148">
+      <c r="I36" s="103" t="s">
+        <v>807</v>
+      </c>
+      <c r="J36" s="103">
         <v>10</v>
       </c>
-      <c r="K36" s="148">
+      <c r="K36" s="103">
         <v>13</v>
       </c>
-      <c r="L36" s="148">
+      <c r="L36" s="103">
         <v>64</v>
       </c>
       <c r="M36" s="67">
@@ -40922,7 +41266,7 @@
         <f t="shared" si="0"/>
         <v>241</v>
       </c>
-      <c r="P36" s="149">
+      <c r="P36" s="104">
         <f t="shared" si="1"/>
         <v>0.30125000000000002</v>
       </c>
@@ -40932,7 +41276,7 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="49">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B37" s="29">
         <v>613</v>
@@ -40977,7 +41321,7 @@
         <f t="shared" si="0"/>
         <v>651</v>
       </c>
-      <c r="P37" s="149">
+      <c r="P37" s="104">
         <f t="shared" si="1"/>
         <v>0.81374999999999997</v>
       </c>
@@ -40986,8 +41330,8 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" s="52">
-        <v>32</v>
+      <c r="A38" s="49">
+        <v>15</v>
       </c>
       <c r="B38" s="29">
         <v>907</v>
@@ -41001,25 +41345,25 @@
       <c r="E38" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F38" s="148">
+      <c r="F38" s="103">
         <v>92</v>
       </c>
-      <c r="G38" s="148">
+      <c r="G38" s="103">
         <v>43</v>
       </c>
-      <c r="H38" s="148">
+      <c r="H38" s="103">
         <v>95</v>
       </c>
-      <c r="I38" s="148">
+      <c r="I38" s="103">
         <v>45</v>
       </c>
-      <c r="J38" s="148">
+      <c r="J38" s="103">
         <v>54</v>
       </c>
-      <c r="K38" s="148">
+      <c r="K38" s="103">
         <v>83</v>
       </c>
-      <c r="L38" s="148">
+      <c r="L38" s="103">
         <v>75</v>
       </c>
       <c r="M38" s="67">
@@ -41032,7 +41376,7 @@
         <f t="shared" si="0"/>
         <v>549</v>
       </c>
-      <c r="P38" s="149">
+      <c r="P38" s="104">
         <f t="shared" si="1"/>
         <v>0.68625000000000003</v>
       </c>
@@ -41041,8 +41385,8 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="52">
-        <v>33</v>
+      <c r="A39" s="49">
+        <v>16</v>
       </c>
       <c r="B39" s="29">
         <v>354</v>
@@ -41087,7 +41431,7 @@
         <f t="shared" si="0"/>
         <v>440</v>
       </c>
-      <c r="P39" s="149">
+      <c r="P39" s="104">
         <f t="shared" si="1"/>
         <v>0.55000000000000004</v>
       </c>
@@ -41097,7 +41441,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="49">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B40" s="29">
         <v>339</v>
@@ -41142,7 +41486,7 @@
         <f t="shared" si="0"/>
         <v>395</v>
       </c>
-      <c r="P40" s="149">
+      <c r="P40" s="104">
         <f t="shared" si="1"/>
         <v>0.49375000000000002</v>
       </c>
@@ -41152,7 +41496,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="49">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="B41" s="29">
         <v>855</v>
@@ -41166,25 +41510,25 @@
       <c r="E41" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F41" s="147">
+      <c r="F41" s="102">
         <v>45</v>
       </c>
-      <c r="G41" s="147">
+      <c r="G41" s="102">
         <v>33</v>
       </c>
-      <c r="H41" s="147">
+      <c r="H41" s="102">
         <v>62</v>
       </c>
-      <c r="I41" s="147">
+      <c r="I41" s="102">
         <v>38</v>
       </c>
-      <c r="J41" s="147">
+      <c r="J41" s="102">
         <v>33</v>
       </c>
-      <c r="K41" s="147">
+      <c r="K41" s="102">
         <v>40</v>
       </c>
-      <c r="L41" s="147">
+      <c r="L41" s="102">
         <v>62</v>
       </c>
       <c r="M41" s="67">
@@ -41197,7 +41541,7 @@
         <f t="shared" si="0"/>
         <v>366</v>
       </c>
-      <c r="P41" s="149">
+      <c r="P41" s="104">
         <f t="shared" si="1"/>
         <v>0.45750000000000002</v>
       </c>
@@ -41207,7 +41551,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="49">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="B42" s="29">
         <v>879</v>
@@ -41252,7 +41596,7 @@
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="P42" s="149">
+      <c r="P42" s="104">
         <f t="shared" si="1"/>
         <v>0.16625000000000001</v>
       </c>
@@ -41262,7 +41606,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="49">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B43" s="29">
         <v>305</v>
@@ -41276,25 +41620,25 @@
       <c r="E43" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F43" s="147">
+      <c r="F43" s="102">
         <v>43</v>
       </c>
-      <c r="G43" s="147">
+      <c r="G43" s="102">
         <v>49</v>
       </c>
-      <c r="H43" s="147">
+      <c r="H43" s="102">
         <v>85</v>
       </c>
-      <c r="I43" s="147">
+      <c r="I43" s="102">
         <v>54</v>
       </c>
-      <c r="J43" s="147">
+      <c r="J43" s="102">
         <v>33</v>
       </c>
-      <c r="K43" s="147">
+      <c r="K43" s="102">
         <v>44</v>
       </c>
-      <c r="L43" s="147">
+      <c r="L43" s="102">
         <v>96</v>
       </c>
       <c r="M43" s="67">
@@ -41307,7 +41651,7 @@
         <f t="shared" si="0"/>
         <v>444</v>
       </c>
-      <c r="P43" s="149">
+      <c r="P43" s="104">
         <f t="shared" si="1"/>
         <v>0.55500000000000005</v>
       </c>
@@ -41317,7 +41661,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="49">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B44" s="29">
         <v>713</v>
@@ -41331,25 +41675,25 @@
       <c r="E44" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="F44" s="148">
+      <c r="F44" s="103">
         <v>85</v>
       </c>
-      <c r="G44" s="148">
+      <c r="G44" s="103">
         <v>47</v>
       </c>
-      <c r="H44" s="148">
+      <c r="H44" s="103">
         <v>94</v>
       </c>
-      <c r="I44" s="148">
+      <c r="I44" s="103">
         <v>66</v>
       </c>
-      <c r="J44" s="148">
+      <c r="J44" s="103">
         <v>60</v>
       </c>
-      <c r="K44" s="148">
+      <c r="K44" s="103">
         <v>79</v>
       </c>
-      <c r="L44" s="148">
+      <c r="L44" s="103">
         <v>92</v>
       </c>
       <c r="M44" s="67">
@@ -41362,7 +41706,7 @@
         <f t="shared" si="0"/>
         <v>605</v>
       </c>
-      <c r="P44" s="149">
+      <c r="P44" s="104">
         <f t="shared" si="1"/>
         <v>0.75624999999999998</v>
       </c>
@@ -41372,7 +41716,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="49">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B45" s="29">
         <v>789</v>
@@ -41417,7 +41761,7 @@
         <f t="shared" si="0"/>
         <v>415</v>
       </c>
-      <c r="P45" s="149">
+      <c r="P45" s="104">
         <f t="shared" si="1"/>
         <v>0.51875000000000004</v>
       </c>
@@ -41427,7 +41771,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="49">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B46" s="29">
         <v>435</v>
@@ -41472,7 +41816,7 @@
         <f t="shared" si="0"/>
         <v>168</v>
       </c>
-      <c r="P46" s="149">
+      <c r="P46" s="104">
         <f t="shared" si="1"/>
         <v>0.21</v>
       </c>
@@ -41482,7 +41826,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="49">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="B47" s="29">
         <v>903</v>
@@ -41527,7 +41871,7 @@
         <f t="shared" si="0"/>
         <v>327</v>
       </c>
-      <c r="P47" s="149">
+      <c r="P47" s="104">
         <f t="shared" si="1"/>
         <v>0.40875</v>
       </c>
@@ -41537,12 +41881,12 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="49">
-        <v>42</v>
-      </c>
-      <c r="B48" s="142">
+        <v>25</v>
+      </c>
+      <c r="B48" s="100">
         <v>446</v>
       </c>
-      <c r="C48" s="143" t="s">
+      <c r="C48" s="101" t="s">
         <v>922</v>
       </c>
       <c r="D48" s="49" t="s">
@@ -41582,7 +41926,7 @@
         <f t="shared" si="0"/>
         <v>222</v>
       </c>
-      <c r="P48" s="149">
+      <c r="P48" s="104">
         <f t="shared" si="1"/>
         <v>0.27750000000000002</v>
       </c>
@@ -41623,5 +41967,6 @@
   <ignoredErrors>
     <ignoredError sqref="O7:O48" formulaRange="1"/>
   </ignoredErrors>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>